--- a/outputs/marine_equipment/Анализ_цен.xlsx
+++ b/outputs/marine_equipment/Анализ_цен.xlsx
@@ -180,8 +180,8 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -602,15 +602,15 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Кристина (Веда)</t>
+          <t>Титов</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.8197</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>цена с НДС 22%, делим на 1,22</t>
+          <t>условия в шапке не указаны, берем как есть — уточнить</t>
         </is>
       </c>
     </row>
@@ -632,22 +632,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ПромВест</t>
+          <t>Андрей Евротрейд</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1</v>
+        <v>0.8197</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>цен пока нет</t>
+          <t>безнал с НДС 22%, делим на 1,22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Андрей Евротрейд</t>
+          <t>Кристина (Веда)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -655,14 +655,14 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>безнал с НДС 22%, делим на 1,22</t>
+          <t>цена с НДС 22%, делим на 1,22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Титов</t>
+          <t>Ленпромарматура</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
@@ -670,37 +670,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>условия в шапке не указаны, берем как есть — уточнить</t>
+          <t>без НДС, февраль 2026, берем как есть</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ленпромарматура</t>
+          <t>Антон Бурыкин</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>без НДС, февраль 2026, берем как есть</t>
+          <t>цена ИП наличными минус 6%, февраль 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Антон Бурыкин</t>
+          <t>ПромВест</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>цена ИП наличными минус 6%, февраль 2026</t>
+          <t>цен пока нет</t>
         </is>
       </c>
     </row>
@@ -756,30 +756,30 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Кристина (Веда)</t>
+          <t>Титов</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.02285714285714286</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1317</v>
+        <v>1831</v>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>на уровне рынка</t>
+          <t>тот же прайс, что у конкурента — не независимая цена</t>
         </is>
       </c>
     </row>
@@ -816,112 +816,116 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>ПромВест</t>
+          <t>Андрей Евротрейд</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0</v>
+        <v>0.1085714285714286</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1431</v>
+      </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>нечего сравнить</t>
+          <t>выше рынка, похоже на цену с наценкой</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Андрей Евротрейд</t>
+          <t>Кристина (Веда)</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.1085714285714286</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>1.33</v>
+        <v>0</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>1.13</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>1431</v>
+        <v>1317</v>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>выше рынка, похоже на цену с наценкой</t>
+          <t>на уровне рынка</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Титов</t>
+          <t>Ленпромарматура</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.06285714285714286</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>5.58</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1831</v>
+        <v>7385</v>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>тот же прайс, что у конкурента — не независимая цена</t>
+          <t>в разы выше рынка — похоже на прайс продавца или цену реализации</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Ленпромарматура</t>
+          <t>Антон Бурыкин</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>0.06285714285714286</v>
+        <v>0.04</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>5.58</v>
+        <v>3.38</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>7385</v>
+        <v>10375</v>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
@@ -932,30 +936,26 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Антон Бурыкин</t>
+          <t>ПромВест</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>10375</v>
-      </c>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="8" t="n"/>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>в разы выше рынка — похоже на прайс продавца или цену реализации</t>
+          <t>нечего сравнить</t>
         </is>
       </c>
     </row>
@@ -1253,37 +1253,37 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
+          <t>Титов</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Гелион</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Андрей Евротрейд</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
           <t>Кристина (Веда)</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Гелион</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Ленпромарматура</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Антон Бурыкин</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>ПромВест</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Андрей Евротрейд</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Титов</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Ленпромарматура</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Антон Бурыкин</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -1524,13 +1524,13 @@
       <c r="G9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="19" t="n">
+        <v>9000</v>
+      </c>
       <c r="I9" s="8" t="n"/>
       <c r="J9" s="8" t="n"/>
       <c r="K9" s="8" t="n"/>
-      <c r="L9" s="19" t="n">
-        <v>9000</v>
-      </c>
+      <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8" t="n"/>
       <c r="O9" s="8" t="n">
@@ -1634,13 +1634,13 @@
       <c r="G11" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="8" t="n"/>
+      <c r="H11" s="19" t="n">
+        <v>7500</v>
+      </c>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
-      <c r="L11" s="19" t="n">
-        <v>7500</v>
-      </c>
+      <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n">
@@ -1793,19 +1793,19 @@
       <c r="G14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="n">
+        <v>6000</v>
+      </c>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M14" s="19" t="n">
+      <c r="L14" s="19" t="n">
         <v>21700</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="M14" s="8" t="n">
         <v>16450</v>
       </c>
+      <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n">
         <v>21700</v>
       </c>
@@ -1860,13 +1860,13 @@
       <c r="G15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="8" t="n"/>
+      <c r="H15" s="19" t="n">
+        <v>6000</v>
+      </c>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
-      <c r="L15" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n">
@@ -2117,13 +2117,13 @@
       <c r="G20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="8" t="n"/>
+      <c r="H20" s="19" t="n">
+        <v>4500</v>
+      </c>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
-      <c r="L20" s="19" t="n">
-        <v>4500</v>
-      </c>
+      <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n">
@@ -2178,13 +2178,13 @@
       <c r="G21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="8" t="n"/>
+      <c r="H21" s="19" t="n">
+        <v>10000</v>
+      </c>
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
-      <c r="L21" s="19" t="n">
-        <v>10000</v>
-      </c>
+      <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n"/>
       <c r="O21" s="8" t="n">
@@ -2337,13 +2337,13 @@
       <c r="G24" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="19" t="n">
+        <v>10000</v>
+      </c>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
-      <c r="L24" s="19" t="n">
-        <v>10000</v>
-      </c>
+      <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n">
@@ -2447,13 +2447,13 @@
       <c r="G26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="8" t="n"/>
+      <c r="H26" s="19" t="n">
+        <v>7500</v>
+      </c>
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
-      <c r="L26" s="19" t="n">
-        <v>7500</v>
-      </c>
+      <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n">
@@ -2606,13 +2606,13 @@
       <c r="G29" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="H29" s="8" t="n"/>
+      <c r="H29" s="19" t="n">
+        <v>12800</v>
+      </c>
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
-      <c r="L29" s="19" t="n">
-        <v>12800</v>
-      </c>
+      <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n">
@@ -2667,13 +2667,13 @@
       <c r="G30" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="H30" s="8" t="n"/>
+      <c r="H30" s="19" t="n">
+        <v>12800</v>
+      </c>
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
-      <c r="L30" s="19" t="n">
-        <v>12800</v>
-      </c>
+      <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n"/>
       <c r="O30" s="8" t="n">
@@ -2728,13 +2728,13 @@
       <c r="G31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="8" t="n"/>
+      <c r="H31" s="19" t="n">
+        <v>10100</v>
+      </c>
       <c r="I31" s="8" t="n"/>
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
-      <c r="L31" s="19" t="n">
-        <v>10100</v>
-      </c>
+      <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="n">
@@ -2789,13 +2789,13 @@
       <c r="G32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="8" t="n"/>
+      <c r="H32" s="19" t="n">
+        <v>9600</v>
+      </c>
       <c r="I32" s="8" t="n"/>
       <c r="J32" s="8" t="n"/>
       <c r="K32" s="8" t="n"/>
-      <c r="L32" s="19" t="n">
-        <v>9600</v>
-      </c>
+      <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n"/>
       <c r="O32" s="8" t="n">
@@ -2850,13 +2850,13 @@
       <c r="G33" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H33" s="8" t="n"/>
+      <c r="H33" s="19" t="n">
+        <v>16000</v>
+      </c>
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
-      <c r="L33" s="19" t="n">
-        <v>16000</v>
-      </c>
+      <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n">
@@ -2911,19 +2911,19 @@
       <c r="G34" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H34" s="8" t="n"/>
+      <c r="H34" s="8" t="n">
+        <v>12800</v>
+      </c>
       <c r="I34" s="8" t="n"/>
       <c r="J34" s="8" t="n"/>
       <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n">
-        <v>12800</v>
-      </c>
-      <c r="M34" s="19" t="n">
+      <c r="L34" s="19" t="n">
         <v>32100</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="M34" s="8" t="n">
         <v>22560</v>
       </c>
+      <c r="N34" s="8" t="n"/>
       <c r="O34" s="8" t="n">
         <v>32100</v>
       </c>
@@ -3064,13 +3064,13 @@
       <c r="G37" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="8" t="n"/>
+      <c r="H37" s="19" t="n">
+        <v>6000</v>
+      </c>
       <c r="I37" s="8" t="n"/>
       <c r="J37" s="8" t="n"/>
       <c r="K37" s="8" t="n"/>
-      <c r="L37" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n"/>
       <c r="O37" s="8" t="n">
@@ -3193,13 +3193,13 @@
       <c r="G40" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H40" s="8" t="n"/>
+      <c r="H40" s="19" t="n">
+        <v>3000</v>
+      </c>
       <c r="I40" s="8" t="n"/>
       <c r="J40" s="8" t="n"/>
       <c r="K40" s="8" t="n"/>
-      <c r="L40" s="19" t="n">
-        <v>3000</v>
-      </c>
+      <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n"/>
       <c r="O40" s="8" t="n">
@@ -3254,19 +3254,19 @@
       <c r="G41" s="8" t="n">
         <v>798</v>
       </c>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="n">
+        <v>4000</v>
+      </c>
       <c r="I41" s="8" t="n"/>
       <c r="J41" s="8" t="n"/>
       <c r="K41" s="8" t="n"/>
-      <c r="L41" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M41" s="19" t="n">
+      <c r="L41" s="19" t="n">
         <v>18150</v>
       </c>
-      <c r="N41" s="8" t="n">
+      <c r="M41" s="8" t="n">
         <v>12690</v>
       </c>
+      <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n">
         <v>18150</v>
       </c>
@@ -3321,13 +3321,13 @@
       <c r="G42" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="8" t="n"/>
+      <c r="H42" s="19" t="n">
+        <v>6000</v>
+      </c>
       <c r="I42" s="8" t="n"/>
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="8" t="n"/>
-      <c r="L42" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n"/>
       <c r="O42" s="8" t="n">
@@ -3378,13 +3378,13 @@
       <c r="G43" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="8" t="n"/>
+      <c r="H43" s="19" t="n">
+        <v>12000</v>
+      </c>
       <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
-      <c r="L43" s="19" t="n">
-        <v>12000</v>
-      </c>
+      <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n"/>
       <c r="O43" s="8" t="n">
@@ -3578,13 +3578,13 @@
       <c r="G47" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="8" t="n"/>
+      <c r="H47" s="19" t="n">
+        <v>6000</v>
+      </c>
       <c r="I47" s="8" t="n"/>
       <c r="J47" s="8" t="n"/>
       <c r="K47" s="8" t="n"/>
-      <c r="L47" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n"/>
       <c r="O47" s="8" t="n">
@@ -3688,13 +3688,13 @@
       <c r="G49" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="H49" s="8" t="n"/>
+      <c r="H49" s="19" t="n">
+        <v>4000</v>
+      </c>
       <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="n"/>
       <c r="K49" s="8" t="n"/>
-      <c r="L49" s="19" t="n">
-        <v>4000</v>
-      </c>
+      <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n"/>
       <c r="O49" s="8" t="n">
@@ -3749,13 +3749,13 @@
       <c r="G50" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H50" s="8" t="n"/>
+      <c r="H50" s="19" t="n">
+        <v>6500</v>
+      </c>
       <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
-      <c r="L50" s="19" t="n">
-        <v>6500</v>
-      </c>
+      <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n"/>
       <c r="O50" s="8" t="n">
@@ -3859,13 +3859,13 @@
       <c r="G52" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H52" s="8" t="n"/>
+      <c r="H52" s="19" t="n">
+        <v>6500</v>
+      </c>
       <c r="I52" s="8" t="n"/>
       <c r="J52" s="8" t="n"/>
       <c r="K52" s="8" t="n"/>
-      <c r="L52" s="19" t="n">
-        <v>6500</v>
-      </c>
+      <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n"/>
       <c r="O52" s="8" t="n">
@@ -3920,13 +3920,13 @@
       <c r="G53" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H53" s="8" t="n"/>
+      <c r="H53" s="19" t="n">
+        <v>4500</v>
+      </c>
       <c r="I53" s="8" t="n"/>
       <c r="J53" s="8" t="n"/>
       <c r="K53" s="8" t="n"/>
-      <c r="L53" s="19" t="n">
-        <v>4500</v>
-      </c>
+      <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n"/>
       <c r="O53" s="8" t="n">
@@ -3981,19 +3981,19 @@
       <c r="G54" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="H54" s="8" t="n"/>
+      <c r="H54" s="8" t="n">
+        <v>4000</v>
+      </c>
       <c r="I54" s="8" t="n"/>
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n"/>
-      <c r="L54" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M54" s="19" t="n">
+      <c r="L54" s="19" t="n">
         <v>23450</v>
       </c>
-      <c r="N54" s="8" t="n">
+      <c r="M54" s="8" t="n">
         <v>12690</v>
       </c>
+      <c r="N54" s="8" t="n"/>
       <c r="O54" s="8" t="n">
         <v>23450</v>
       </c>
@@ -4048,13 +4048,13 @@
       <c r="G55" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H55" s="8" t="n"/>
+      <c r="H55" s="19" t="n">
+        <v>6000</v>
+      </c>
       <c r="I55" s="8" t="n"/>
       <c r="J55" s="8" t="n"/>
       <c r="K55" s="8" t="n"/>
-      <c r="L55" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n"/>
       <c r="O55" s="8" t="n">
@@ -4109,13 +4109,13 @@
       <c r="G56" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="H56" s="8" t="n"/>
+      <c r="H56" s="19" t="n">
+        <v>4000</v>
+      </c>
       <c r="I56" s="8" t="n"/>
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
-      <c r="L56" s="19" t="n">
-        <v>4000</v>
-      </c>
+      <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n"/>
       <c r="O56" s="8" t="n">
@@ -4170,13 +4170,13 @@
       <c r="G57" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H57" s="8" t="n"/>
+      <c r="H57" s="19" t="n">
+        <v>4000</v>
+      </c>
       <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
-      <c r="L57" s="19" t="n">
-        <v>4000</v>
-      </c>
+      <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n"/>
       <c r="O57" s="8" t="n">
@@ -4231,16 +4231,16 @@
       <c r="G58" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H58" s="8" t="n"/>
+      <c r="H58" s="8" t="n">
+        <v>4000</v>
+      </c>
       <c r="I58" s="8" t="n"/>
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
-      <c r="L58" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M58" s="19" t="n">
+      <c r="L58" s="19" t="n">
         <v>23900</v>
       </c>
+      <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n"/>
       <c r="O58" s="8" t="n">
         <v>23900</v>
@@ -4296,13 +4296,13 @@
       <c r="G59" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="8" t="n"/>
+      <c r="H59" s="19" t="n">
+        <v>2500</v>
+      </c>
       <c r="I59" s="8" t="n"/>
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
-      <c r="L59" s="19" t="n">
-        <v>2500</v>
-      </c>
+      <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n"/>
       <c r="O59" s="8" t="n">
@@ -4398,13 +4398,13 @@
       <c r="G61" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H61" s="8" t="n"/>
+      <c r="H61" s="19" t="n">
+        <v>6400</v>
+      </c>
       <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
-      <c r="L61" s="19" t="n">
-        <v>6400</v>
-      </c>
+      <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n"/>
       <c r="O61" s="8" t="n">
@@ -4486,13 +4486,13 @@
       <c r="G63" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H63" s="8" t="n"/>
+      <c r="H63" s="19" t="n">
+        <v>6000</v>
+      </c>
       <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
-      <c r="L63" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n"/>
       <c r="O63" s="8" t="n">
@@ -4547,13 +4547,13 @@
       <c r="G64" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="H64" s="8" t="n"/>
+      <c r="H64" s="19" t="n">
+        <v>6000</v>
+      </c>
       <c r="I64" s="8" t="n"/>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
-      <c r="L64" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n"/>
       <c r="O64" s="8" t="n">
@@ -4602,23 +4602,23 @@
       <c r="G65" s="8" t="n">
         <v>124</v>
       </c>
-      <c r="H65" s="8" t="n"/>
+      <c r="H65" s="8" t="n">
+        <v>6000</v>
+      </c>
       <c r="I65" s="8" t="n">
         <v>5280</v>
       </c>
-      <c r="J65" s="8" t="n"/>
-      <c r="K65" s="8" t="n">
+      <c r="J65" s="8" t="n">
         <v>3689</v>
       </c>
-      <c r="L65" s="8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M65" s="19" t="n">
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="19" t="n">
         <v>30700</v>
       </c>
-      <c r="N65" s="8" t="n">
+      <c r="M65" s="8" t="n">
         <v>11280</v>
       </c>
+      <c r="N65" s="8" t="n"/>
       <c r="O65" s="8" t="n">
         <v>30700</v>
       </c>
@@ -4906,13 +4906,13 @@
       <c r="G71" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="H71" s="8" t="n"/>
+      <c r="H71" s="19" t="n">
+        <v>9600</v>
+      </c>
       <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
-      <c r="L71" s="19" t="n">
-        <v>9600</v>
-      </c>
+      <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n"/>
       <c r="O71" s="8" t="n">
@@ -5256,10 +5256,10 @@
       <c r="I79" s="19" t="n">
         <v>17600</v>
       </c>
-      <c r="J79" s="8" t="n"/>
-      <c r="K79" s="8" t="n">
+      <c r="J79" s="8" t="n">
         <v>14754</v>
       </c>
+      <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
       <c r="M79" s="8" t="n"/>
       <c r="N79" s="8" t="n"/>
@@ -5366,14 +5366,14 @@
       <c r="I81" s="8" t="n">
         <v>26400</v>
       </c>
-      <c r="J81" s="8" t="n"/>
-      <c r="K81" s="8" t="n">
+      <c r="J81" s="8" t="n">
         <v>28689</v>
       </c>
-      <c r="L81" s="8" t="n"/>
-      <c r="M81" s="19" t="n">
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="19" t="n">
         <v>116150</v>
       </c>
+      <c r="M81" s="8" t="n"/>
       <c r="N81" s="8" t="n"/>
       <c r="O81" s="8" t="n">
         <v>116150</v>
@@ -5425,16 +5425,16 @@
       <c r="G82" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H82" s="8" t="n"/>
+      <c r="H82" s="8" t="n">
+        <v>27500</v>
+      </c>
       <c r="I82" s="8" t="n"/>
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
-      <c r="L82" s="8" t="n">
-        <v>27500</v>
-      </c>
-      <c r="M82" s="19" t="n">
+      <c r="L82" s="19" t="n">
         <v>105900</v>
       </c>
+      <c r="M82" s="8" t="n"/>
       <c r="N82" s="8" t="n"/>
       <c r="O82" s="8" t="n">
         <v>105900</v>
@@ -5531,13 +5531,13 @@
       <c r="G84" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="19" t="n">
+        <v>17500</v>
+      </c>
       <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
-      <c r="L84" s="19" t="n">
-        <v>17500</v>
-      </c>
+      <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
       <c r="N84" s="8" t="n"/>
       <c r="O84" s="8" t="n">
@@ -5592,13 +5592,13 @@
       <c r="G85" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H85" s="8" t="n"/>
+      <c r="H85" s="19" t="n">
+        <v>29000</v>
+      </c>
       <c r="I85" s="8" t="n"/>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
-      <c r="L85" s="19" t="n">
-        <v>29000</v>
-      </c>
+      <c r="L85" s="8" t="n"/>
       <c r="M85" s="8" t="n"/>
       <c r="N85" s="8" t="n"/>
       <c r="O85" s="8" t="n">
@@ -5792,17 +5792,17 @@
       <c r="G89" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="n">
+        <v>40000</v>
+      </c>
       <c r="I89" s="19" t="n">
         <v>48400</v>
       </c>
-      <c r="J89" s="8" t="n"/>
-      <c r="K89" s="8" t="n">
+      <c r="J89" s="8" t="n">
         <v>39344</v>
       </c>
-      <c r="L89" s="8" t="n">
-        <v>40000</v>
-      </c>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
       <c r="N89" s="8" t="n"/>
       <c r="O89" s="8" t="n">
@@ -5855,13 +5855,13 @@
       <c r="G90" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H90" s="8" t="n"/>
+      <c r="H90" s="19" t="n">
+        <v>55000</v>
+      </c>
       <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
-      <c r="L90" s="19" t="n">
-        <v>55000</v>
-      </c>
+      <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
       <c r="N90" s="8" t="n"/>
       <c r="O90" s="8" t="n">
@@ -5912,13 +5912,13 @@
       <c r="G91" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H91" s="8" t="n"/>
+      <c r="H91" s="19" t="n">
+        <v>60000</v>
+      </c>
       <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
-      <c r="L91" s="19" t="n">
-        <v>60000</v>
-      </c>
+      <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n"/>
       <c r="O91" s="8" t="n">
@@ -6035,17 +6035,17 @@
       <c r="G94" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="H94" s="8" t="n"/>
+      <c r="H94" s="19" t="n">
+        <v>27500</v>
+      </c>
       <c r="I94" s="8" t="n">
         <v>26400</v>
       </c>
-      <c r="J94" s="8" t="n"/>
-      <c r="K94" s="8" t="n">
+      <c r="J94" s="8" t="n">
         <v>22951</v>
       </c>
-      <c r="L94" s="19" t="n">
-        <v>27500</v>
-      </c>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n"/>
       <c r="O94" s="8" t="n">
@@ -6200,15 +6200,15 @@
       <c r="G97" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="H97" s="8" t="n"/>
+      <c r="H97" s="8" t="n">
+        <v>23000</v>
+      </c>
       <c r="I97" s="19" t="n">
         <v>42240</v>
       </c>
       <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
-      <c r="L97" s="8" t="n">
-        <v>23000</v>
-      </c>
+      <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n"/>
       <c r="O97" s="8" t="n">
@@ -6314,13 +6314,13 @@
       <c r="G99" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="19" t="n">
+        <v>28000</v>
+      </c>
       <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
-      <c r="L99" s="19" t="n">
-        <v>28000</v>
-      </c>
+      <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n"/>
       <c r="O99" s="8" t="n">
@@ -6469,15 +6469,15 @@
       <c r="G102" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H102" s="8" t="n"/>
+      <c r="H102" s="8" t="n">
+        <v>45000</v>
+      </c>
       <c r="I102" s="19" t="n">
         <v>96800</v>
       </c>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
-      <c r="L102" s="8" t="n">
-        <v>45000</v>
-      </c>
+      <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n"/>
       <c r="O102" s="8" t="n">
@@ -6534,13 +6534,13 @@
       <c r="G103" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H103" s="8" t="n"/>
+      <c r="H103" s="19" t="n">
+        <v>56200</v>
+      </c>
       <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
-      <c r="L103" s="19" t="n">
-        <v>56200</v>
-      </c>
+      <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n"/>
       <c r="O103" s="8" t="n">
@@ -6706,13 +6706,13 @@
       <c r="G107" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="H107" s="8" t="n"/>
+      <c r="H107" s="19" t="n">
+        <v>32000</v>
+      </c>
       <c r="I107" s="8" t="n"/>
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
-      <c r="L107" s="19" t="n">
-        <v>32000</v>
-      </c>
+      <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n"/>
       <c r="O107" s="8" t="n">
@@ -6767,13 +6767,13 @@
       <c r="G108" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H108" s="8" t="n"/>
+      <c r="H108" s="19" t="n">
+        <v>15000</v>
+      </c>
       <c r="I108" s="8" t="n"/>
       <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
-      <c r="L108" s="19" t="n">
-        <v>15000</v>
-      </c>
+      <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n"/>
       <c r="O108" s="8" t="n">
@@ -6828,13 +6828,13 @@
       <c r="G109" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H109" s="8" t="n"/>
+      <c r="H109" s="19" t="n">
+        <v>19500</v>
+      </c>
       <c r="I109" s="8" t="n"/>
       <c r="J109" s="8" t="n"/>
       <c r="K109" s="8" t="n"/>
-      <c r="L109" s="19" t="n">
-        <v>19500</v>
-      </c>
+      <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
       <c r="N109" s="8" t="n"/>
       <c r="O109" s="8" t="n">
@@ -6889,13 +6889,13 @@
       <c r="G110" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H110" s="8" t="n"/>
+      <c r="H110" s="19" t="n">
+        <v>9750</v>
+      </c>
       <c r="I110" s="8" t="n"/>
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
-      <c r="L110" s="19" t="n">
-        <v>9750</v>
-      </c>
+      <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
       <c r="N110" s="8" t="n"/>
       <c r="O110" s="8" t="n">
@@ -6950,13 +6950,13 @@
       <c r="G111" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H111" s="8" t="n"/>
+      <c r="H111" s="19" t="n">
+        <v>39000</v>
+      </c>
       <c r="I111" s="8" t="n"/>
       <c r="J111" s="8" t="n"/>
       <c r="K111" s="8" t="n"/>
-      <c r="L111" s="19" t="n">
-        <v>39000</v>
-      </c>
+      <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
       <c r="N111" s="8" t="n"/>
       <c r="O111" s="8" t="n">
@@ -7011,13 +7011,13 @@
       <c r="G112" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H112" s="8" t="n"/>
+      <c r="H112" s="19" t="n">
+        <v>80000</v>
+      </c>
       <c r="I112" s="8" t="n"/>
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
-      <c r="L112" s="19" t="n">
-        <v>80000</v>
-      </c>
+      <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
       <c r="N112" s="8" t="n"/>
       <c r="O112" s="8" t="n">
@@ -7174,16 +7174,16 @@
         <v>36</v>
       </c>
       <c r="H116" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I116" s="8" t="n"/>
+      <c r="J116" s="19" t="n">
+        <v>34426</v>
+      </c>
+      <c r="K116" s="8" t="n">
         <v>28689</v>
       </c>
-      <c r="I116" s="8" t="n"/>
-      <c r="J116" s="8" t="n"/>
-      <c r="K116" s="19" t="n">
-        <v>34426</v>
-      </c>
-      <c r="L116" s="8" t="n">
-        <v>30000</v>
-      </c>
+      <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
       <c r="N116" s="8" t="n"/>
       <c r="O116" s="8" t="n">
@@ -7236,21 +7236,21 @@
       <c r="G117" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H117" s="8" t="n"/>
+      <c r="H117" s="8" t="n">
+        <v>37500</v>
+      </c>
       <c r="I117" s="8" t="n"/>
-      <c r="J117" s="8" t="n"/>
-      <c r="K117" s="8" t="n">
+      <c r="J117" s="8" t="n">
         <v>40984</v>
       </c>
-      <c r="L117" s="8" t="n">
-        <v>37500</v>
-      </c>
-      <c r="M117" s="19" t="n">
+      <c r="K117" s="8" t="n"/>
+      <c r="L117" s="19" t="n">
         <v>189200</v>
       </c>
-      <c r="N117" s="8" t="n">
+      <c r="M117" s="8" t="n">
         <v>84600</v>
       </c>
+      <c r="N117" s="8" t="n"/>
       <c r="O117" s="8" t="n">
         <v>189200</v>
       </c>
@@ -7305,13 +7305,13 @@
       <c r="I118" s="8" t="n"/>
       <c r="J118" s="8" t="n"/>
       <c r="K118" s="8" t="n"/>
-      <c r="L118" s="8" t="n"/>
-      <c r="M118" s="19" t="n">
+      <c r="L118" s="19" t="n">
         <v>221150</v>
       </c>
-      <c r="N118" s="8" t="n">
+      <c r="M118" s="8" t="n">
         <v>136300</v>
       </c>
+      <c r="N118" s="8" t="n"/>
       <c r="O118" s="8" t="n">
         <v>221150</v>
       </c>
@@ -7356,17 +7356,17 @@
       <c r="G119" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="H119" s="8" t="n">
+      <c r="H119" s="19" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I119" s="8" t="n"/>
+      <c r="J119" s="8" t="n">
+        <v>143443</v>
+      </c>
+      <c r="K119" s="8" t="n">
         <v>118852</v>
       </c>
-      <c r="I119" s="8" t="n"/>
-      <c r="J119" s="8" t="n"/>
-      <c r="K119" s="8" t="n">
-        <v>143443</v>
-      </c>
-      <c r="L119" s="19" t="n">
-        <v>150000</v>
-      </c>
+      <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
       <c r="N119" s="8" t="n"/>
       <c r="O119" s="8" t="n">
@@ -7420,16 +7420,16 @@
         <v>19</v>
       </c>
       <c r="H120" s="8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I120" s="8" t="n"/>
+      <c r="J120" s="19" t="n">
+        <v>163934</v>
+      </c>
+      <c r="K120" s="8" t="n">
         <v>139344</v>
       </c>
-      <c r="I120" s="8" t="n"/>
-      <c r="J120" s="8" t="n"/>
-      <c r="K120" s="19" t="n">
-        <v>163934</v>
-      </c>
-      <c r="L120" s="8" t="n">
-        <v>150000</v>
-      </c>
+      <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n"/>
       <c r="O120" s="8" t="n">
@@ -7482,13 +7482,13 @@
       <c r="G121" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H121" s="8" t="n"/>
+      <c r="H121" s="19" t="n">
+        <v>75000</v>
+      </c>
       <c r="I121" s="8" t="n"/>
       <c r="J121" s="8" t="n"/>
       <c r="K121" s="8" t="n"/>
-      <c r="L121" s="19" t="n">
-        <v>75000</v>
-      </c>
+      <c r="L121" s="8" t="n"/>
       <c r="M121" s="8" t="n"/>
       <c r="N121" s="8" t="n"/>
       <c r="O121" s="8" t="n">
@@ -7539,18 +7539,18 @@
       <c r="G122" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="H122" s="8" t="n">
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="8" t="n"/>
+      <c r="J122" s="8" t="n">
+        <v>245902</v>
+      </c>
+      <c r="K122" s="8" t="n">
         <v>286885</v>
       </c>
-      <c r="I122" s="8" t="n"/>
-      <c r="J122" s="8" t="n"/>
-      <c r="K122" s="8" t="n">
-        <v>245902</v>
-      </c>
-      <c r="L122" s="8" t="n"/>
-      <c r="M122" s="19" t="n">
+      <c r="L122" s="19" t="n">
         <v>588100</v>
       </c>
+      <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n"/>
       <c r="O122" s="8" t="n">
         <v>588100</v>
@@ -7760,15 +7760,15 @@
       <c r="G127" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H127" s="8" t="n"/>
+      <c r="H127" s="19" t="n">
+        <v>45000</v>
+      </c>
       <c r="I127" s="8" t="n"/>
-      <c r="J127" s="8" t="n"/>
-      <c r="K127" s="8" t="n">
+      <c r="J127" s="8" t="n">
         <v>40984</v>
       </c>
-      <c r="L127" s="19" t="n">
-        <v>45000</v>
-      </c>
+      <c r="K127" s="8" t="n"/>
+      <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n"/>
       <c r="O127" s="8" t="n">
@@ -7860,10 +7860,10 @@
       </c>
       <c r="H129" s="8" t="n"/>
       <c r="I129" s="8" t="n"/>
-      <c r="J129" s="8" t="n"/>
-      <c r="K129" s="19" t="n">
+      <c r="J129" s="19" t="n">
         <v>81967</v>
       </c>
+      <c r="K129" s="8" t="n"/>
       <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n"/>
@@ -7919,13 +7919,13 @@
       <c r="G130" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H130" s="8" t="n"/>
+      <c r="H130" s="19" t="n">
+        <v>90000</v>
+      </c>
       <c r="I130" s="8" t="n"/>
       <c r="J130" s="8" t="n"/>
       <c r="K130" s="8" t="n"/>
-      <c r="L130" s="19" t="n">
-        <v>90000</v>
-      </c>
+      <c r="L130" s="8" t="n"/>
       <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n"/>
       <c r="O130" s="8" t="n">
@@ -8015,15 +8015,15 @@
       <c r="G132" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H132" s="8" t="n"/>
+      <c r="H132" s="19" t="n">
+        <v>250000</v>
+      </c>
       <c r="I132" s="8" t="n"/>
-      <c r="J132" s="8" t="n"/>
-      <c r="K132" s="8" t="n">
+      <c r="J132" s="8" t="n">
         <v>163934</v>
       </c>
-      <c r="L132" s="19" t="n">
-        <v>250000</v>
-      </c>
+      <c r="K132" s="8" t="n"/>
+      <c r="L132" s="8" t="n"/>
       <c r="M132" s="8" t="n"/>
       <c r="N132" s="8" t="n"/>
       <c r="O132" s="8" t="n">
@@ -8207,13 +8207,13 @@
       <c r="G136" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H136" s="8" t="n"/>
+      <c r="H136" s="19" t="n">
+        <v>22500</v>
+      </c>
       <c r="I136" s="8" t="n"/>
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
-      <c r="L136" s="19" t="n">
-        <v>22500</v>
-      </c>
+      <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n"/>
       <c r="O136" s="8" t="n">
@@ -8264,13 +8264,13 @@
       <c r="G137" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H137" s="8" t="n"/>
+      <c r="H137" s="19" t="n">
+        <v>30000</v>
+      </c>
       <c r="I137" s="8" t="n"/>
       <c r="J137" s="8" t="n"/>
       <c r="K137" s="8" t="n"/>
-      <c r="L137" s="19" t="n">
-        <v>30000</v>
-      </c>
+      <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n"/>
       <c r="O137" s="8" t="n">
@@ -8854,13 +8854,13 @@
       <c r="G151" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H151" s="8" t="n"/>
+      <c r="H151" s="19" t="n">
+        <v>9000</v>
+      </c>
       <c r="I151" s="8" t="n"/>
       <c r="J151" s="8" t="n"/>
       <c r="K151" s="8" t="n"/>
-      <c r="L151" s="19" t="n">
-        <v>9000</v>
-      </c>
+      <c r="L151" s="8" t="n"/>
       <c r="M151" s="8" t="n"/>
       <c r="N151" s="8" t="n"/>
       <c r="O151" s="8" t="n">
@@ -8991,13 +8991,13 @@
       <c r="G154" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H154" s="8" t="n"/>
+      <c r="H154" s="19" t="n">
+        <v>25000</v>
+      </c>
       <c r="I154" s="8" t="n"/>
       <c r="J154" s="8" t="n"/>
       <c r="K154" s="8" t="n"/>
-      <c r="L154" s="19" t="n">
-        <v>25000</v>
-      </c>
+      <c r="L154" s="8" t="n"/>
       <c r="M154" s="8" t="n"/>
       <c r="N154" s="8" t="n"/>
       <c r="O154" s="8" t="n">
@@ -9259,17 +9259,17 @@
       <c r="G160" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H160" s="8" t="n"/>
+      <c r="H160" s="19" t="n">
+        <v>60000</v>
+      </c>
       <c r="I160" s="8" t="n">
         <v>48400</v>
       </c>
-      <c r="J160" s="8" t="n"/>
-      <c r="K160" s="8" t="n">
+      <c r="J160" s="8" t="n">
         <v>40984</v>
       </c>
-      <c r="L160" s="19" t="n">
-        <v>60000</v>
-      </c>
+      <c r="K160" s="8" t="n"/>
+      <c r="L160" s="8" t="n"/>
       <c r="M160" s="8" t="n"/>
       <c r="N160" s="8" t="n"/>
       <c r="O160" s="8" t="n">
@@ -9322,15 +9322,15 @@
       <c r="G161" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H161" s="8" t="n"/>
+      <c r="H161" s="19" t="n">
+        <v>90000</v>
+      </c>
       <c r="I161" s="8" t="n"/>
-      <c r="J161" s="8" t="n"/>
-      <c r="K161" s="8" t="n">
+      <c r="J161" s="8" t="n">
         <v>61475</v>
       </c>
-      <c r="L161" s="19" t="n">
-        <v>90000</v>
-      </c>
+      <c r="K161" s="8" t="n"/>
+      <c r="L161" s="8" t="n"/>
       <c r="M161" s="8" t="n"/>
       <c r="N161" s="8" t="n"/>
       <c r="O161" s="8" t="n">
@@ -9383,17 +9383,17 @@
       <c r="G162" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="H162" s="8" t="n"/>
+      <c r="H162" s="8" t="n">
+        <v>57600</v>
+      </c>
       <c r="I162" s="19" t="n">
         <v>83600</v>
       </c>
-      <c r="J162" s="8" t="n"/>
-      <c r="K162" s="8" t="n">
+      <c r="J162" s="8" t="n">
         <v>61475</v>
       </c>
-      <c r="L162" s="8" t="n">
-        <v>57600</v>
-      </c>
+      <c r="K162" s="8" t="n"/>
+      <c r="L162" s="8" t="n"/>
       <c r="M162" s="8" t="n"/>
       <c r="N162" s="8" t="n"/>
       <c r="O162" s="8" t="n">
@@ -9446,15 +9446,15 @@
       <c r="G163" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H163" s="8" t="n"/>
+      <c r="H163" s="8" t="n">
+        <v>84000</v>
+      </c>
       <c r="I163" s="8" t="n"/>
-      <c r="J163" s="8" t="n"/>
-      <c r="K163" s="19" t="n">
+      <c r="J163" s="19" t="n">
         <v>94262</v>
       </c>
-      <c r="L163" s="8" t="n">
-        <v>84000</v>
-      </c>
+      <c r="K163" s="8" t="n"/>
+      <c r="L163" s="8" t="n"/>
       <c r="M163" s="8" t="n"/>
       <c r="N163" s="8" t="n"/>
       <c r="O163" s="8" t="n">
@@ -9511,10 +9511,10 @@
       <c r="I164" s="19" t="n">
         <v>132000</v>
       </c>
-      <c r="J164" s="8" t="n"/>
-      <c r="K164" s="8" t="n">
+      <c r="J164" s="8" t="n">
         <v>106557</v>
       </c>
+      <c r="K164" s="8" t="n"/>
       <c r="L164" s="8" t="n"/>
       <c r="M164" s="8" t="n"/>
       <c r="N164" s="8" t="n"/>
@@ -9640,13 +9640,13 @@
       <c r="G167" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H167" s="8" t="n"/>
+      <c r="H167" s="19" t="n">
+        <v>9000</v>
+      </c>
       <c r="I167" s="8" t="n"/>
       <c r="J167" s="8" t="n"/>
       <c r="K167" s="8" t="n"/>
-      <c r="L167" s="19" t="n">
-        <v>9000</v>
-      </c>
+      <c r="L167" s="8" t="n"/>
       <c r="M167" s="8" t="n"/>
       <c r="N167" s="8" t="n"/>
       <c r="O167" s="8" t="n">
@@ -9750,13 +9750,13 @@
       <c r="G169" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="H169" s="8" t="n"/>
+      <c r="H169" s="19" t="n">
+        <v>8000</v>
+      </c>
       <c r="I169" s="8" t="n"/>
       <c r="J169" s="8" t="n"/>
       <c r="K169" s="8" t="n"/>
-      <c r="L169" s="19" t="n">
-        <v>8000</v>
-      </c>
+      <c r="L169" s="8" t="n"/>
       <c r="M169" s="8" t="n"/>
       <c r="N169" s="8" t="n"/>
       <c r="O169" s="8" t="n">
@@ -9811,13 +9811,13 @@
       <c r="G170" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H170" s="8" t="n"/>
+      <c r="H170" s="19" t="n">
+        <v>16000</v>
+      </c>
       <c r="I170" s="8" t="n"/>
       <c r="J170" s="8" t="n"/>
       <c r="K170" s="8" t="n"/>
-      <c r="L170" s="19" t="n">
-        <v>16000</v>
-      </c>
+      <c r="L170" s="8" t="n"/>
       <c r="M170" s="8" t="n"/>
       <c r="N170" s="8" t="n"/>
       <c r="O170" s="8" t="n">
@@ -9872,15 +9872,15 @@
       <c r="G171" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H171" s="8" t="n"/>
+      <c r="H171" s="19" t="n">
+        <v>14400</v>
+      </c>
       <c r="I171" s="8" t="n">
         <v>12320</v>
       </c>
       <c r="J171" s="8" t="n"/>
       <c r="K171" s="8" t="n"/>
-      <c r="L171" s="19" t="n">
-        <v>14400</v>
-      </c>
+      <c r="L171" s="8" t="n"/>
       <c r="M171" s="8" t="n"/>
       <c r="N171" s="8" t="n"/>
       <c r="O171" s="8" t="n">
@@ -9937,13 +9937,13 @@
       <c r="G172" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H172" s="8" t="n"/>
+      <c r="H172" s="19" t="n">
+        <v>9600</v>
+      </c>
       <c r="I172" s="8" t="n"/>
       <c r="J172" s="8" t="n"/>
       <c r="K172" s="8" t="n"/>
-      <c r="L172" s="19" t="n">
-        <v>9600</v>
-      </c>
+      <c r="L172" s="8" t="n"/>
       <c r="M172" s="8" t="n"/>
       <c r="N172" s="8" t="n"/>
       <c r="O172" s="8" t="n">
@@ -9998,13 +9998,13 @@
       <c r="G173" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H173" s="8" t="n"/>
+      <c r="H173" s="19" t="n">
+        <v>25000</v>
+      </c>
       <c r="I173" s="8" t="n"/>
       <c r="J173" s="8" t="n"/>
       <c r="K173" s="8" t="n"/>
-      <c r="L173" s="19" t="n">
-        <v>25000</v>
-      </c>
+      <c r="L173" s="8" t="n"/>
       <c r="M173" s="8" t="n"/>
       <c r="N173" s="8" t="n"/>
       <c r="O173" s="8" t="n">
@@ -10059,13 +10059,13 @@
       <c r="G174" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H174" s="8" t="n"/>
+      <c r="H174" s="19" t="n">
+        <v>19500</v>
+      </c>
       <c r="I174" s="8" t="n"/>
       <c r="J174" s="8" t="n"/>
       <c r="K174" s="8" t="n"/>
-      <c r="L174" s="19" t="n">
-        <v>19500</v>
-      </c>
+      <c r="L174" s="8" t="n"/>
       <c r="M174" s="8" t="n"/>
       <c r="N174" s="8" t="n"/>
       <c r="O174" s="8" t="n">
@@ -10685,13 +10685,13 @@
       <c r="G190" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H190" s="8" t="n"/>
+      <c r="H190" s="19" t="n">
+        <v>12000</v>
+      </c>
       <c r="I190" s="8" t="n"/>
       <c r="J190" s="8" t="n"/>
       <c r="K190" s="8" t="n"/>
-      <c r="L190" s="19" t="n">
-        <v>12000</v>
-      </c>
+      <c r="L190" s="8" t="n"/>
       <c r="M190" s="8" t="n"/>
       <c r="N190" s="8" t="n"/>
       <c r="O190" s="8" t="n">
@@ -10847,17 +10847,17 @@
       <c r="G194" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H194" s="8" t="n"/>
+      <c r="H194" s="8" t="n">
+        <v>12000</v>
+      </c>
       <c r="I194" s="19" t="n">
         <v>22000</v>
       </c>
-      <c r="J194" s="8" t="n"/>
-      <c r="K194" s="8" t="n">
+      <c r="J194" s="8" t="n">
         <v>16393</v>
       </c>
-      <c r="L194" s="8" t="n">
-        <v>12000</v>
-      </c>
+      <c r="K194" s="8" t="n"/>
+      <c r="L194" s="8" t="n"/>
       <c r="M194" s="8" t="n"/>
       <c r="N194" s="8" t="n"/>
       <c r="O194" s="8" t="n">
@@ -10908,13 +10908,13 @@
       <c r="G195" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="H195" s="8" t="n"/>
+      <c r="H195" s="19" t="n">
+        <v>18000</v>
+      </c>
       <c r="I195" s="8" t="n"/>
       <c r="J195" s="8" t="n"/>
       <c r="K195" s="8" t="n"/>
-      <c r="L195" s="19" t="n">
-        <v>18000</v>
-      </c>
+      <c r="L195" s="8" t="n"/>
       <c r="M195" s="8" t="n"/>
       <c r="N195" s="8" t="n"/>
       <c r="O195" s="8" t="n">
@@ -10984,13 +10984,13 @@
       <c r="G197" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H197" s="8" t="n"/>
+      <c r="H197" s="19" t="n">
+        <v>30000</v>
+      </c>
       <c r="I197" s="8" t="n"/>
       <c r="J197" s="8" t="n"/>
       <c r="K197" s="8" t="n"/>
-      <c r="L197" s="19" t="n">
-        <v>30000</v>
-      </c>
+      <c r="L197" s="8" t="n"/>
       <c r="M197" s="8" t="n"/>
       <c r="N197" s="8" t="n"/>
       <c r="O197" s="8" t="n">
@@ -11109,13 +11109,13 @@
       <c r="G200" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H200" s="8" t="n"/>
+      <c r="H200" s="19" t="n">
+        <v>9600</v>
+      </c>
       <c r="I200" s="8" t="n"/>
       <c r="J200" s="8" t="n"/>
       <c r="K200" s="8" t="n"/>
-      <c r="L200" s="19" t="n">
-        <v>9600</v>
-      </c>
+      <c r="L200" s="8" t="n"/>
       <c r="M200" s="8" t="n"/>
       <c r="N200" s="8" t="n"/>
       <c r="O200" s="8" t="n">
@@ -14477,37 +14477,37 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Титов</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Гелион</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Андрей Евротрейд</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>Кристина (Веда)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Гелион</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Ленпромарматура</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Антон Бурыкин</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>ПромВест</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Андрей Евротрейд</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Титов</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Ленпромарматура</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Антон Бурыкин</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -14533,37 +14533,37 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
+          <t>15 поз  3 226 руб/кг</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>2 поз  10 850 руб/кг</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>2 поз  8 225 руб/кг</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t>15 поз  3 226 руб/кг</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  10 850 руб/кг</t>
-        </is>
-      </c>
-      <c r="K5" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  8 225 руб/кг</t>
         </is>
       </c>
       <c r="L5" s="14" t="n">
@@ -14587,37 +14587,37 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
+          <t>16 поз  2 462 руб/кг</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>3 поз  11 381 руб/кг</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>2 поз  10 575 руб/кг</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>16 поз  2 462 руб/кг</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t>3 поз  11 381 руб/кг</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  10 575 руб/кг</t>
         </is>
       </c>
       <c r="L6" s="14" t="n">
@@ -14641,37 +14641,37 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
+          <t>4 поз  8 571 руб/кг</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  7 543 руб/кг</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  5 269 руб/кг</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  7 543 руб/кг</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  43 857 руб/кг</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  16 114 руб/кг</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  5 269 руб/кг</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>4 поз  8 571 руб/кг</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  43 857 руб/кг</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  16 114 руб/кг</t>
         </is>
       </c>
       <c r="L7" s="14" t="n">
@@ -14695,35 +14695,35 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
+          <t>5 поз  1 902 руб/кг</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>3 поз  2 839 руб/кг</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>3 поз  2 544 руб/кг</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>3 поз  2 839 руб/кг</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>2 поз  12 489 руб/кг</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>3 поз  2 544 руб/кг</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>5 поз  1 902 руб/кг</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  12 489 руб/кг</t>
-        </is>
-      </c>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14749,35 +14749,35 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
+          <t>5 поз  1 292 руб/кг</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>3 поз  2 200 руб/кг</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  1 913 руб/кг</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>3 поз  2 200 руб/кг</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  1 913 руб/кг</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>5 поз  1 292 руб/кг</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14803,35 +14803,35 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
+          <t>6 поз  2 222 руб/кг</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>6 поз  2 222 руб/кг</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14855,39 +14855,39 @@
       <c r="D11" s="21" t="n">
         <v>7394</v>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>5 поз  1 370 руб/кг</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>5 поз  1 448 руб/кг</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>4 поз  1 351 руб/кг</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>3 поз  5 945 руб/кг</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>2 поз  3 664 руб/кг</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>5 поз  1 448 руб/кг</t>
-        </is>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>5 поз  1 370 руб/кг</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t>3 поз  5 945 руб/кг</t>
-        </is>
-      </c>
-      <c r="K11" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  3 664 руб/кг</t>
         </is>
       </c>
       <c r="L11" s="14" t="n">
@@ -14911,35 +14911,35 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
+          <t>2 поз  2 000 руб/кг</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  2 712 руб/кг</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>2 поз  1 952 руб/кг</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  2 712 руб/кг</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  1 952 руб/кг</t>
-        </is>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  2 000 руб/кг</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14965,35 +14965,35 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
+          <t>2 поз  3 191 руб/кг</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  3 191 руб/кг</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15017,37 +15017,37 @@
       <c r="D14" s="21" t="n">
         <v>401</v>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15075,35 +15075,35 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
+          <t>1 поз  1 364 руб/кг</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  1 364 руб/кг</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15129,35 +15129,35 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
+          <t>1 поз  2 232 руб/кг</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  3 169 руб/кг</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  3 169 руб/кг</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  2 232 руб/кг</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="J16" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15183,35 +15183,35 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
+          <t>4 поз  2 000 руб/кг</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>3 поз  1 613 руб/кг</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>5 поз  1 366 руб/кг</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>3 поз  1 613 руб/кг</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t>5 поз  1 366 руб/кг</t>
-        </is>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>4 поз  2 000 руб/кг</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15237,35 +15237,35 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
+          <t>7 поз  3 200 руб/кг</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  3 005 руб/кг</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  3 005 руб/кг</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>7 поз  3 200 руб/кг</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K18" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15289,37 +15289,37 @@
       <c r="D19" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J19" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="K19" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15345,37 +15345,37 @@
       <c r="D20" s="21" t="n">
         <v>110</v>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="J20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K20" s="22" t="inlineStr">
+      <c r="K20" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15401,37 +15401,37 @@
       <c r="D21" s="21" t="n">
         <v>258</v>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J21" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K21" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15457,37 +15457,37 @@
       <c r="D22" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="J22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr">
+      <c r="K22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15515,35 +15515,35 @@
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
+          <t>1 поз  1 034 руб/кг</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  1 034 руб/кг</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J23" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K23" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15569,35 +15569,35 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
+          <t>2 поз  3 273 руб/кг</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  4 000 руб/кг</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>1 поз  2 981 руб/кг</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  4 000 руб/кг</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  2 981 руб/кг</t>
-        </is>
-      </c>
-      <c r="I24" s="23" t="inlineStr">
-        <is>
-          <t>2 поз  3 273 руб/кг</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15625,35 +15625,35 @@
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
+          <t>1 поз  7 500 руб/кг</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  7 500 руб/кг</t>
-        </is>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K25" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15681,35 +15681,35 @@
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
+          <t>1 поз  2 043 руб/кг</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I26" s="23" t="inlineStr">
-        <is>
-          <t>1 поз  2 043 руб/кг</t>
-        </is>
-      </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/outputs/marine_equipment/Анализ_цен.xlsx
+++ b/outputs/marine_equipment/Анализ_цен.xlsx
@@ -1424,12 +1424,12 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>НАША ЦЕНА продажи</t>
+          <t>НАША ЦЕНА продажи по договору</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Наша цена по договору</t>
+          <t>Справочно: цена по учету склада</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
-          <t>Максимум к нашей цене</t>
+          <t>Максимум к цене по договору</t>
         </is>
       </c>
       <c r="Z4" s="4" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>Штуцерная угловая — 33 позиции, с ценой 15  наша цена 1 224-7 692 руб/кг  предложения 1 531-10 850</t>
+          <t>Штуцерная угловая — 33 позиции, с ценой 15  наша цена по договору 1 724-11 538 руб/кг  предложения 1 531-10 850</t>
         </is>
       </c>
       <c r="B5" s="19" t="n"/>
@@ -1578,10 +1578,10 @@
       <c r="G6" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="I6" s="8" t="n"/>
       <c r="J6" s="8" t="n">
         <v>760</v>
       </c>
@@ -1637,10 +1637,10 @@
         <v>6</v>
       </c>
       <c r="H7" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I7" s="8" t="n">
         <v>4000</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>3000</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>350</v>
@@ -1697,10 +1697,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I8" s="8" t="n">
         <v>7500</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>5000</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>650</v>
@@ -1756,10 +1756,10 @@
       <c r="G9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="8" t="n">
+      <c r="H9" s="22" t="n">
         <v>6500</v>
       </c>
+      <c r="I9" s="8" t="n"/>
       <c r="J9" s="8" t="n">
         <v>22</v>
       </c>
@@ -1795,7 +1795,9 @@
       <c r="X9" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="Y9" s="12" t="n"/>
+      <c r="Y9" s="10" t="n">
+        <v>1.384615384615385</v>
+      </c>
       <c r="Z9" s="8" t="n">
         <v>400</v>
       </c>
@@ -1828,10 +1830,10 @@
       <c r="G10" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n">
         <v>2150</v>
       </c>
@@ -1886,10 +1888,10 @@
       <c r="G11" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n">
         <v>2450</v>
       </c>
@@ -1925,9 +1927,7 @@
       <c r="X11" s="10" t="n">
         <v>1531</v>
       </c>
-      <c r="Y11" s="10" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="Y11" s="12" t="n"/>
       <c r="Z11" s="8" t="n">
         <v>3.061224489795918</v>
       </c>
@@ -1960,10 +1960,10 @@
       <c r="G12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n">
         <v>1000</v>
       </c>
@@ -2276,10 +2276,10 @@
       <c r="G17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n">
         <v>1000</v>
       </c>
@@ -2335,10 +2335,10 @@
         <v>2</v>
       </c>
       <c r="H18" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I18" s="8" t="n">
         <v>4800</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>10000</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>900</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I19" s="8" t="n">
         <v>3000</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>4000</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>950</v>
@@ -2455,10 +2455,10 @@
         <v>1</v>
       </c>
       <c r="H20" s="22" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I20" s="8" t="n">
         <v>9000</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>4500</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>900</v>
@@ -2495,8 +2495,8 @@
       <c r="X20" s="10" t="n">
         <v>2500</v>
       </c>
-      <c r="Y20" s="13" t="n">
-        <v>0.5</v>
+      <c r="Y20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="Z20" s="8" t="n">
         <v>5</v>
@@ -2531,10 +2531,10 @@
         <v>1</v>
       </c>
       <c r="H21" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I21" s="8" t="n">
         <v>7500</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>5000</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>1450</v>
@@ -2572,7 +2572,7 @@
         <v>3448</v>
       </c>
       <c r="Y21" s="10" t="n">
-        <v>1.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="Z21" s="8" t="n">
         <v>6.896551724137931</v>
@@ -2606,10 +2606,10 @@
       <c r="G22" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="8" t="n">
         <v>7500</v>
       </c>
-      <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n">
         <v>1550</v>
       </c>
@@ -2720,10 +2720,10 @@
       <c r="G24" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="22" t="n">
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="8" t="n">
         <v>7500</v>
       </c>
-      <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n">
         <v>1550</v>
       </c>
@@ -2759,9 +2759,7 @@
       <c r="X24" s="10" t="n">
         <v>3226</v>
       </c>
-      <c r="Y24" s="10" t="n">
-        <v>1.333333333333333</v>
-      </c>
+      <c r="Y24" s="12" t="n"/>
       <c r="Z24" s="8" t="n">
         <v>6.451612903225806</v>
       </c>
@@ -2850,10 +2848,10 @@
       <c r="G26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="8" t="n">
         <v>10500</v>
       </c>
-      <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n">
         <v>1550</v>
       </c>
@@ -2889,9 +2887,7 @@
       <c r="X26" s="10" t="n">
         <v>2419</v>
       </c>
-      <c r="Y26" s="13" t="n">
-        <v>0.7142857142857143</v>
-      </c>
+      <c r="Y26" s="12" t="n"/>
       <c r="Z26" s="8" t="n">
         <v>4.838709677419355</v>
       </c>
@@ -2980,10 +2976,10 @@
       <c r="G28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="8" t="n">
         <v>10500</v>
       </c>
-      <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n">
         <v>1550</v>
       </c>
@@ -3039,10 +3035,10 @@
         <v>31</v>
       </c>
       <c r="H29" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I29" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>1650</v>
@@ -3080,7 +3076,7 @@
         <v>3879</v>
       </c>
       <c r="Y29" s="10" t="n">
-        <v>1.333333333333333</v>
+        <v>1.969230769230769</v>
       </c>
       <c r="Z29" s="8" t="n">
         <v>7.757575757575758</v>
@@ -3115,10 +3111,10 @@
         <v>14</v>
       </c>
       <c r="H30" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I30" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>1650</v>
@@ -3156,7 +3152,7 @@
         <v>3879</v>
       </c>
       <c r="Y30" s="10" t="n">
-        <v>1.333333333333333</v>
+        <v>1.969230769230769</v>
       </c>
       <c r="Z30" s="8" t="n">
         <v>7.757575757575758</v>
@@ -3191,10 +3187,10 @@
         <v>1</v>
       </c>
       <c r="H31" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I31" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>1650</v>
@@ -3232,7 +3228,7 @@
         <v>3061</v>
       </c>
       <c r="Y31" s="10" t="n">
-        <v>1.052083333333333</v>
+        <v>1.553846153846154</v>
       </c>
       <c r="Z31" s="8" t="n">
         <v>6.121212121212121</v>
@@ -3267,10 +3263,10 @@
         <v>1</v>
       </c>
       <c r="H32" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I32" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>1650</v>
@@ -3308,7 +3304,7 @@
         <v>2909</v>
       </c>
       <c r="Y32" s="10" t="n">
-        <v>1</v>
+        <v>1.476923076923077</v>
       </c>
       <c r="Z32" s="8" t="n">
         <v>5.818181818181818</v>
@@ -3342,10 +3338,10 @@
       <c r="G33" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H33" s="22" t="n">
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="8" t="n">
         <v>9600</v>
       </c>
-      <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n">
         <v>1950</v>
       </c>
@@ -3381,9 +3377,7 @@
       <c r="X33" s="10" t="n">
         <v>4103</v>
       </c>
-      <c r="Y33" s="10" t="n">
-        <v>1.666666666666667</v>
-      </c>
+      <c r="Y33" s="12" t="n"/>
       <c r="Z33" s="8" t="n">
         <v>8.205128205128204</v>
       </c>
@@ -3417,10 +3411,10 @@
         <v>8</v>
       </c>
       <c r="H34" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I34" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>1850</v>
@@ -3464,7 +3458,7 @@
         <v>8676</v>
       </c>
       <c r="Y34" s="10" t="n">
-        <v>3.34375</v>
+        <v>4.938461538461539</v>
       </c>
       <c r="Z34" s="8" t="n">
         <v>17.35135135135135</v>
@@ -3499,10 +3493,10 @@
         <v>3</v>
       </c>
       <c r="H35" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I35" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>1850</v>
@@ -3559,10 +3553,10 @@
         <v>4</v>
       </c>
       <c r="H36" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I36" s="8" t="n">
         <v>10000</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>650</v>
@@ -3675,10 +3669,10 @@
         <v>8</v>
       </c>
       <c r="H38" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I38" s="8" t="n">
         <v>4000</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>3000</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>500</v>
@@ -3703,7 +3697,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>Штуцерная проходная — 22 позиции, с ценой 16  наша цена 1 579-3 571 руб/кг  предложения 1 304-15 125</t>
+          <t>Штуцерная проходная — 22 позиции, с ценой 16  наша цена по договору 2 500-5 495 руб/кг  предложения 1 304-15 125</t>
         </is>
       </c>
       <c r="B39" s="19" t="n"/>
@@ -3760,10 +3754,10 @@
       <c r="G40" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H40" s="22" t="n">
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="8" t="n">
         <v>4000</v>
       </c>
-      <c r="I40" s="8" t="n"/>
       <c r="J40" s="8" t="n">
         <v>1150</v>
       </c>
@@ -3799,9 +3793,7 @@
       <c r="X40" s="10" t="n">
         <v>1304</v>
       </c>
-      <c r="Y40" s="13" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="Y40" s="12" t="n"/>
       <c r="Z40" s="8" t="n">
         <v>2.608695652173913</v>
       </c>
@@ -3835,10 +3827,10 @@
         <v>798</v>
       </c>
       <c r="H41" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I41" s="8" t="n">
         <v>3000</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>4000</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>600</v>
@@ -3882,7 +3874,7 @@
         <v>15125</v>
       </c>
       <c r="Y41" s="10" t="n">
-        <v>6.05</v>
+        <v>4.5375</v>
       </c>
       <c r="Z41" s="8" t="n">
         <v>30.25</v>
@@ -3917,10 +3909,10 @@
         <v>1</v>
       </c>
       <c r="H42" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I42" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I42" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>1900</v>
@@ -3957,8 +3949,8 @@
       <c r="X42" s="10" t="n">
         <v>1579</v>
       </c>
-      <c r="Y42" s="10" t="n">
-        <v>1</v>
+      <c r="Y42" s="13" t="n">
+        <v>0.3</v>
       </c>
       <c r="Z42" s="8" t="n">
         <v>3.157894736842105</v>
@@ -3989,10 +3981,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I43" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>1820</v>
@@ -4029,8 +4021,8 @@
       <c r="X43" s="10" t="n">
         <v>3297</v>
       </c>
-      <c r="Y43" s="10" t="n">
-        <v>2</v>
+      <c r="Y43" s="13" t="n">
+        <v>0.6</v>
       </c>
       <c r="Z43" s="8" t="n">
         <v>6.593406593406593</v>
@@ -4064,10 +4056,10 @@
       <c r="G44" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="8" t="n">
+      <c r="H44" s="22" t="n">
         <v>4000</v>
       </c>
+      <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="n">
         <v>400</v>
       </c>
@@ -4170,10 +4162,10 @@
       <c r="G46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="22" t="n">
+      <c r="H46" s="22" t="n"/>
+      <c r="I46" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="I46" s="8" t="n"/>
       <c r="J46" s="8" t="n"/>
       <c r="K46" s="8" t="n"/>
       <c r="L46" s="8" t="n"/>
@@ -4226,10 +4218,10 @@
       <c r="G47" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="22" t="n">
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I47" s="8" t="n"/>
       <c r="J47" s="8" t="n">
         <v>1150</v>
       </c>
@@ -4265,9 +4257,7 @@
       <c r="X47" s="10" t="n">
         <v>2609</v>
       </c>
-      <c r="Y47" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y47" s="12" t="n"/>
       <c r="Z47" s="8" t="n">
         <v>5.217391304347826</v>
       </c>
@@ -4300,10 +4290,10 @@
       <c r="G48" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="22" t="n">
+      <c r="H48" s="22" t="n"/>
+      <c r="I48" s="8" t="n">
         <v>7500</v>
       </c>
-      <c r="I48" s="8" t="n"/>
       <c r="J48" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4358,10 +4348,10 @@
       <c r="G49" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="H49" s="22" t="n">
+      <c r="H49" s="22" t="n"/>
+      <c r="I49" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4397,9 +4387,7 @@
       <c r="X49" s="10" t="n">
         <v>1905</v>
       </c>
-      <c r="Y49" s="13" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+      <c r="Y49" s="12" t="n"/>
       <c r="Z49" s="8" t="n">
         <v>3.809523809523809</v>
       </c>
@@ -4432,10 +4420,10 @@
       <c r="G50" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H50" s="22" t="n">
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4471,9 +4459,7 @@
       <c r="X50" s="10" t="n">
         <v>3095</v>
       </c>
-      <c r="Y50" s="10" t="n">
-        <v>1.083333333333333</v>
-      </c>
+      <c r="Y50" s="12" t="n"/>
       <c r="Z50" s="8" t="n">
         <v>6.190476190476191</v>
       </c>
@@ -4506,10 +4492,10 @@
       <c r="G51" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="22" t="n">
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I51" s="8" t="n"/>
       <c r="J51" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4564,10 +4550,10 @@
       <c r="G52" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H52" s="22" t="n">
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I52" s="8" t="n"/>
       <c r="J52" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4603,9 +4589,7 @@
       <c r="X52" s="10" t="n">
         <v>3095</v>
       </c>
-      <c r="Y52" s="10" t="n">
-        <v>1.083333333333333</v>
-      </c>
+      <c r="Y52" s="12" t="n"/>
       <c r="Z52" s="8" t="n">
         <v>6.190476190476191</v>
       </c>
@@ -4638,10 +4622,10 @@
       <c r="G53" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H53" s="22" t="n">
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I53" s="8" t="n"/>
       <c r="J53" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4677,9 +4661,7 @@
       <c r="X53" s="10" t="n">
         <v>2143</v>
       </c>
-      <c r="Y53" s="13" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="Y53" s="12" t="n"/>
       <c r="Z53" s="8" t="n">
         <v>4.285714285714286</v>
       </c>
@@ -4712,10 +4694,10 @@
       <c r="G54" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="H54" s="22" t="n">
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I54" s="8" t="n"/>
       <c r="J54" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4757,9 +4739,7 @@
       <c r="X54" s="10" t="n">
         <v>11167</v>
       </c>
-      <c r="Y54" s="10" t="n">
-        <v>3.908333333333333</v>
-      </c>
+      <c r="Y54" s="12" t="n"/>
       <c r="Z54" s="8" t="n">
         <v>22.33333333333333</v>
       </c>
@@ -4862,10 +4842,10 @@
       <c r="G56" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="H56" s="22" t="n">
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I56" s="8" t="n"/>
       <c r="J56" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4901,9 +4881,7 @@
       <c r="X56" s="10" t="n">
         <v>1905</v>
       </c>
-      <c r="Y56" s="13" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+      <c r="Y56" s="12" t="n"/>
       <c r="Z56" s="8" t="n">
         <v>3.809523809523809</v>
       </c>
@@ -4936,10 +4914,10 @@
       <c r="G57" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H57" s="22" t="n">
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="n">
         <v>1050</v>
       </c>
@@ -4975,9 +4953,7 @@
       <c r="X57" s="10" t="n">
         <v>1905</v>
       </c>
-      <c r="Y57" s="13" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+      <c r="Y57" s="12" t="n"/>
       <c r="Z57" s="8" t="n">
         <v>3.809523809523809</v>
       </c>
@@ -5010,10 +4986,10 @@
       <c r="G58" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H58" s="22" t="n">
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I58" s="8" t="n"/>
       <c r="J58" s="8" t="n">
         <v>1050</v>
       </c>
@@ -5053,9 +5029,7 @@
       <c r="X58" s="10" t="n">
         <v>11381</v>
       </c>
-      <c r="Y58" s="10" t="n">
-        <v>3.983333333333333</v>
-      </c>
+      <c r="Y58" s="12" t="n"/>
       <c r="Z58" s="8" t="n">
         <v>22.76190476190476</v>
       </c>
@@ -5089,10 +5063,10 @@
         <v>2</v>
       </c>
       <c r="H59" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I59" s="8" t="n">
         <v>1250</v>
-      </c>
-      <c r="I59" s="8" t="n">
-        <v>1500</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>300</v>
@@ -5130,7 +5104,7 @@
         <v>4167</v>
       </c>
       <c r="Y59" s="10" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Z59" s="8" t="n">
         <v>8.333333333333334</v>
@@ -5156,10 +5130,10 @@
       <c r="G60" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="22" t="n">
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="I60" s="8" t="n"/>
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
@@ -5257,7 +5231,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан — 12 позиций, с ценой 4  наша цена 1 286-8 571 руб/кг  предложения 1 745-43 857</t>
+          <t>Штуцерная, угол или проход не указан — 12 позиций, с ценой 4  наша цена по договору 2 823-13 158 руб/кг  предложения 1 745-43 857</t>
         </is>
       </c>
       <c r="B62" s="19" t="n"/>
@@ -5314,10 +5288,10 @@
       <c r="G63" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H63" s="22" t="n">
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n">
         <v>550</v>
       </c>
@@ -5353,9 +5327,7 @@
       <c r="X63" s="10" t="n">
         <v>5455</v>
       </c>
-      <c r="Y63" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y63" s="12" t="n"/>
       <c r="Z63" s="8" t="n">
         <v>10.90909090909091</v>
       </c>
@@ -5389,10 +5361,10 @@
         <v>18</v>
       </c>
       <c r="H64" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I64" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I64" s="8" t="n">
-        <v>3500</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>350</v>
@@ -5424,7 +5396,7 @@
         <v>8571</v>
       </c>
       <c r="Y64" s="10" t="n">
-        <v>1</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="Z64" s="8" t="n">
         <v>17.14285714285714</v>
@@ -5459,10 +5431,10 @@
         <v>124</v>
       </c>
       <c r="H65" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I65" s="8" t="n">
         <v>4500</v>
-      </c>
-      <c r="I65" s="8" t="n">
-        <v>3500</v>
       </c>
       <c r="J65" s="8" t="n">
         <v>350</v>
@@ -5510,7 +5482,7 @@
         <v>43857</v>
       </c>
       <c r="Y65" s="10" t="n">
-        <v>6.822222222222222</v>
+        <v>8.771428571428572</v>
       </c>
       <c r="Z65" s="8" t="n">
         <v>87.71428571428571</v>
@@ -5545,10 +5517,10 @@
         <v>1</v>
       </c>
       <c r="H66" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I66" s="8" t="n">
         <v>4500</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>1750</v>
@@ -5598,10 +5570,10 @@
       <c r="G67" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H67" s="22" t="n">
+      <c r="H67" s="22" t="n"/>
+      <c r="I67" s="8" t="n">
         <v>4500</v>
       </c>
-      <c r="I67" s="8" t="n"/>
       <c r="J67" s="8" t="n">
         <v>1030</v>
       </c>
@@ -5657,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="H68" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I68" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>3500</v>
       </c>
       <c r="J68" s="8" t="n">
         <v>385</v>
@@ -5717,10 +5689,10 @@
         <v>1</v>
       </c>
       <c r="H69" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I69" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I69" s="8" t="n">
-        <v>3500</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>620</v>
@@ -5776,10 +5748,10 @@
       <c r="G70" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="22" t="n"/>
-      <c r="I70" s="8" t="n">
+      <c r="H70" s="22" t="n">
         <v>17500</v>
       </c>
+      <c r="I70" s="8" t="n"/>
       <c r="J70" s="8" t="n">
         <v>2750</v>
       </c>
@@ -5828,10 +5800,10 @@
       <c r="G71" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="H71" s="22" t="n"/>
-      <c r="I71" s="8" t="n">
+      <c r="H71" s="22" t="n">
         <v>17500</v>
       </c>
+      <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n">
         <v>2750</v>
       </c>
@@ -5861,7 +5833,9 @@
       <c r="X71" s="10" t="n">
         <v>1745</v>
       </c>
-      <c r="Y71" s="12" t="n"/>
+      <c r="Y71" s="13" t="n">
+        <v>0.5485714285714286</v>
+      </c>
       <c r="Z71" s="8" t="n">
         <v>3.490909090909091</v>
       </c>
@@ -5895,10 +5869,10 @@
         <v>1</v>
       </c>
       <c r="H72" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I72" s="8" t="n">
         <v>10000</v>
-      </c>
-      <c r="I72" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J72" s="8" t="n">
         <v>760</v>
@@ -5948,10 +5922,10 @@
       <c r="G73" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H73" s="22" t="n"/>
-      <c r="I73" s="8" t="n">
+      <c r="H73" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="n">
         <v>2850</v>
       </c>
@@ -6000,10 +5974,10 @@
       <c r="G74" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H74" s="22" t="n"/>
-      <c r="I74" s="8" t="n">
+      <c r="H74" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="I74" s="8" t="n"/>
       <c r="J74" s="8" t="n">
         <v>2850</v>
       </c>
@@ -6027,7 +6001,7 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>Фланцевая угловая — 17 позиций, с ценой 8  наша цена 1 360-1 745 руб/кг  предложения 1 812-12 489</t>
+          <t>Фланцевая угловая — 17 позиций, с ценой 8  наша цена по договору 1 200-3 636 руб/кг  предложения 1 812-12 489</t>
         </is>
       </c>
       <c r="B75" s="19" t="n"/>
@@ -6085,10 +6059,10 @@
         <v>13</v>
       </c>
       <c r="H76" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I76" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I76" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J76" s="8" t="n">
         <v>2750</v>
@@ -6139,10 +6113,10 @@
         <v>1</v>
       </c>
       <c r="H77" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I77" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="I77" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J77" s="8" t="n">
         <v>2750</v>
@@ -6516,10 +6490,10 @@
       <c r="G83" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="22" t="n">
+      <c r="H83" s="22" t="n"/>
+      <c r="I83" s="8" t="n">
         <v>22500</v>
       </c>
-      <c r="I83" s="8" t="n"/>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
@@ -6639,10 +6613,10 @@
         <v>3</v>
       </c>
       <c r="H85" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I85" s="8" t="n">
         <v>27000</v>
-      </c>
-      <c r="I85" s="8" t="n">
-        <v>25000</v>
       </c>
       <c r="J85" s="8" t="n">
         <v>8000</v>
@@ -6680,7 +6654,7 @@
         <v>1812</v>
       </c>
       <c r="Y85" s="10" t="n">
-        <v>1.074074074074074</v>
+        <v>1.16</v>
       </c>
       <c r="Z85" s="8" t="n">
         <v>3.625</v>
@@ -6711,10 +6685,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I86" s="8" t="n">
         <v>27000</v>
-      </c>
-      <c r="I86" s="8" t="n">
-        <v>25000</v>
       </c>
       <c r="J86" s="8" t="n">
         <v>8000</v>
@@ -6767,10 +6741,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I87" s="8" t="n">
         <v>27000</v>
-      </c>
-      <c r="I87" s="8" t="n">
-        <v>25000</v>
       </c>
       <c r="J87" s="8" t="n">
         <v>8000</v>
@@ -6883,10 +6857,10 @@
         <v>28</v>
       </c>
       <c r="H89" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I89" s="8" t="n">
         <v>34000</v>
-      </c>
-      <c r="I89" s="8" t="n">
-        <v>30000</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>12500</v>
@@ -6930,7 +6904,7 @@
         <v>1936</v>
       </c>
       <c r="Y89" s="10" t="n">
-        <v>1.423529411764706</v>
+        <v>1.613333333333333</v>
       </c>
       <c r="Z89" s="8" t="n">
         <v>3.872</v>
@@ -7027,10 +7001,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I91" s="8" t="n">
         <v>80000</v>
-      </c>
-      <c r="I91" s="8" t="n">
-        <v>50000</v>
       </c>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="23" t="n">
@@ -7063,8 +7037,8 @@
         </is>
       </c>
       <c r="X91" s="12" t="n"/>
-      <c r="Y91" s="13" t="n">
-        <v>0.75</v>
+      <c r="Y91" s="10" t="n">
+        <v>1.2</v>
       </c>
       <c r="Z91" s="8" t="n"/>
     </row>
@@ -7089,10 +7063,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I92" s="8" t="n">
         <v>80000</v>
-      </c>
-      <c r="I92" s="8" t="n">
-        <v>50000</v>
       </c>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
@@ -7121,7 +7095,7 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>Фланцевая проходная — 12 позиций, с ценой 5  наша цена 815-1 875 руб/кг  предложения 1 222-2 373</t>
+          <t>Фланцевая проходная — 12 позиций, с ценой 5  наша цена по договору 1 196-8 571 руб/кг  предложения 1 222-2 373</t>
         </is>
       </c>
       <c r="B93" s="19" t="n"/>
@@ -7175,10 +7149,10 @@
         <v>51</v>
       </c>
       <c r="H94" s="22" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I94" s="8" t="n">
         <v>22500</v>
-      </c>
-      <c r="I94" s="8" t="n">
-        <v>17500</v>
       </c>
       <c r="J94" s="8" t="n">
         <v>6000</v>
@@ -7222,7 +7196,7 @@
         <v>2292</v>
       </c>
       <c r="Y94" s="10" t="n">
-        <v>1.222222222222222</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="Z94" s="8" t="n">
         <v>4.583333333333333</v>
@@ -7312,10 +7286,10 @@
       <c r="G96" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H96" s="22" t="n"/>
-      <c r="I96" s="8" t="n">
+      <c r="H96" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="I96" s="8" t="n"/>
       <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
@@ -7564,10 +7538,10 @@
       <c r="G100" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H100" s="22" t="n"/>
-      <c r="I100" s="8" t="n">
+      <c r="H100" s="22" t="n">
         <v>47500</v>
       </c>
+      <c r="I100" s="8" t="n"/>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
@@ -7673,10 +7647,10 @@
         <v>2</v>
       </c>
       <c r="H102" s="22" t="n">
+        <v>55000</v>
+      </c>
+      <c r="I102" s="8" t="n">
         <v>37500</v>
-      </c>
-      <c r="I102" s="8" t="n">
-        <v>55000</v>
       </c>
       <c r="J102" s="8" t="n">
         <v>23000</v>
@@ -7718,7 +7692,7 @@
         <v>2104</v>
       </c>
       <c r="Y102" s="10" t="n">
-        <v>2.581333333333333</v>
+        <v>1.76</v>
       </c>
       <c r="Z102" s="8" t="n">
         <v>4.208695652173913</v>
@@ -7752,10 +7726,10 @@
       <c r="G103" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H103" s="22" t="n"/>
-      <c r="I103" s="8" t="n">
+      <c r="H103" s="22" t="n">
         <v>55000</v>
       </c>
+      <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n">
         <v>23000</v>
       </c>
@@ -7791,7 +7765,9 @@
       <c r="X103" s="10" t="n">
         <v>1222</v>
       </c>
-      <c r="Y103" s="12" t="n"/>
+      <c r="Y103" s="10" t="n">
+        <v>1.021818181818182</v>
+      </c>
       <c r="Z103" s="8" t="n">
         <v>2.443478260869565</v>
       </c>
@@ -7820,10 +7796,10 @@
       <c r="G104" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H104" s="22" t="n"/>
-      <c r="I104" s="8" t="n">
+      <c r="H104" s="22" t="n">
         <v>55000</v>
       </c>
+      <c r="I104" s="8" t="n"/>
       <c r="J104" s="8" t="n">
         <v>23000</v>
       </c>
@@ -7874,10 +7850,10 @@
       <c r="G105" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H105" s="22" t="n">
+      <c r="H105" s="22" t="n"/>
+      <c r="I105" s="8" t="n">
         <v>150000</v>
       </c>
-      <c r="I105" s="8" t="n"/>
       <c r="J105" s="8" t="n">
         <v>55000</v>
       </c>
@@ -7901,7 +7877,7 @@
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="19" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан — 6 позиций, с ценой 6  наша цена 1 250-2 261 руб/кг  предложения 1 389-2 783</t>
+          <t>Фланцевая, угол или проход не указан — 6 позиций, с ценой 6  предложения 1 389-2 783</t>
         </is>
       </c>
       <c r="B106" s="19" t="n"/>
@@ -7958,10 +7934,10 @@
       <c r="G107" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="H107" s="22" t="n">
+      <c r="H107" s="22" t="n"/>
+      <c r="I107" s="8" t="n">
         <v>26000</v>
       </c>
-      <c r="I107" s="8" t="n"/>
       <c r="J107" s="8" t="n">
         <v>5750</v>
       </c>
@@ -7997,9 +7973,7 @@
       <c r="X107" s="10" t="n">
         <v>2783</v>
       </c>
-      <c r="Y107" s="10" t="n">
-        <v>1.230769230769231</v>
-      </c>
+      <c r="Y107" s="12" t="n"/>
       <c r="Z107" s="8" t="n">
         <v>5.565217391304348</v>
       </c>
@@ -8242,10 +8216,10 @@
       <c r="G111" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H111" s="22" t="n">
+      <c r="H111" s="22" t="n"/>
+      <c r="I111" s="8" t="n">
         <v>35000</v>
       </c>
-      <c r="I111" s="8" t="n"/>
       <c r="J111" s="8" t="n">
         <v>11250</v>
       </c>
@@ -8281,9 +8255,7 @@
       <c r="X111" s="10" t="n">
         <v>1733</v>
       </c>
-      <c r="Y111" s="10" t="n">
-        <v>1.114285714285714</v>
-      </c>
+      <c r="Y111" s="12" t="n"/>
       <c r="Z111" s="8" t="n">
         <v>3.466666666666667</v>
       </c>
@@ -8316,10 +8288,10 @@
       <c r="G112" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H112" s="22" t="n">
+      <c r="H112" s="22" t="n"/>
+      <c r="I112" s="8" t="n">
         <v>45000</v>
       </c>
-      <c r="I112" s="8" t="n"/>
       <c r="J112" s="8" t="n">
         <v>18000</v>
       </c>
@@ -8355,9 +8327,7 @@
       <c r="X112" s="10" t="n">
         <v>2222</v>
       </c>
-      <c r="Y112" s="10" t="n">
-        <v>1.777777777777778</v>
-      </c>
+      <c r="Y112" s="12" t="n"/>
       <c r="Z112" s="8" t="n">
         <v>4.444444444444445</v>
       </c>
@@ -8365,7 +8335,7 @@
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="19" t="inlineStr">
         <is>
-          <t>Клинкеты — 10 позиций, с ценой 7  наша цена 1 096-1 705 руб/кг  предложения 1 311-6 686</t>
+          <t>Клинкеты — 10 позиций, с ценой 7  наша цена по договору 964-1 206 руб/кг  предложения 1 311-6 686</t>
         </is>
       </c>
       <c r="B113" s="19" t="n"/>
@@ -8510,10 +8480,10 @@
       <c r="G116" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="H116" s="22" t="n">
+      <c r="H116" s="22" t="n"/>
+      <c r="I116" s="8" t="n">
         <v>24000</v>
       </c>
-      <c r="I116" s="8" t="n"/>
       <c r="J116" s="8" t="n">
         <v>10950</v>
       </c>
@@ -8555,9 +8525,7 @@
       <c r="X116" s="10" t="n">
         <v>1572</v>
       </c>
-      <c r="Y116" s="10" t="n">
-        <v>1.434426229508197</v>
-      </c>
+      <c r="Y116" s="12" t="n"/>
       <c r="Z116" s="8" t="n">
         <v>3.143947900291938</v>
       </c>
@@ -8725,10 +8693,10 @@
         <v>15</v>
       </c>
       <c r="H119" s="22" t="n">
+        <v>87500</v>
+      </c>
+      <c r="I119" s="8" t="n">
         <v>150000</v>
-      </c>
-      <c r="I119" s="8" t="n">
-        <v>87500</v>
       </c>
       <c r="J119" s="8" t="n">
         <v>44000</v>
@@ -8772,7 +8740,7 @@
         <v>1705</v>
       </c>
       <c r="Y119" s="10" t="n">
-        <v>1</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="Z119" s="8" t="n">
         <v>3.409090909090909</v>
@@ -8803,10 +8771,10 @@
         <v>19</v>
       </c>
       <c r="H120" s="22" t="n">
+        <v>140000</v>
+      </c>
+      <c r="I120" s="8" t="n">
         <v>200000</v>
-      </c>
-      <c r="I120" s="8" t="n">
-        <v>140000</v>
       </c>
       <c r="J120" s="8" t="n">
         <v>62500</v>
@@ -8849,8 +8817,8 @@
       <c r="X120" s="10" t="n">
         <v>1311</v>
       </c>
-      <c r="Y120" s="13" t="n">
-        <v>0.8196721311475411</v>
+      <c r="Y120" s="10" t="n">
+        <v>1.17096018735363</v>
       </c>
       <c r="Z120" s="8" t="n">
         <v>2.622950819672131</v>
@@ -8947,10 +8915,10 @@
         <v>13</v>
       </c>
       <c r="H122" s="22" t="n">
+        <v>185000</v>
+      </c>
+      <c r="I122" s="8" t="n">
         <v>250000</v>
-      </c>
-      <c r="I122" s="8" t="n">
-        <v>185000</v>
       </c>
       <c r="J122" s="8" t="n">
         <v>96000</v>
@@ -8988,7 +8956,7 @@
         <v>3063</v>
       </c>
       <c r="Y122" s="10" t="n">
-        <v>2.3524</v>
+        <v>3.178918918918919</v>
       </c>
       <c r="Z122" s="8" t="n">
         <v>6.126041666666667</v>
@@ -9019,10 +8987,10 @@
         <v>1</v>
       </c>
       <c r="H123" s="22" t="n">
+        <v>275000</v>
+      </c>
+      <c r="I123" s="8" t="n">
         <v>300000</v>
-      </c>
-      <c r="I123" s="8" t="n">
-        <v>275000</v>
       </c>
       <c r="J123" s="8" t="n">
         <v>114000</v>
@@ -9047,7 +9015,7 @@
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="19" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды — 9 позиций, с ценой 5  наша цена 2 326-2 857 руб/кг  предложения 1 689-2 712</t>
+          <t>Фильтры забортной воды — 9 позиций, с ценой 5  наша цена по договору 1 081-8 393 руб/кг  предложения 1 689-2 712</t>
         </is>
       </c>
       <c r="B124" s="19" t="n"/>
@@ -9213,10 +9181,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I127" s="8" t="n">
         <v>60000</v>
-      </c>
-      <c r="I127" s="8" t="n">
-        <v>30000</v>
       </c>
       <c r="J127" s="8" t="n"/>
       <c r="K127" s="23" t="n">
@@ -9253,8 +9221,8 @@
         </is>
       </c>
       <c r="X127" s="12" t="n"/>
-      <c r="Y127" s="13" t="n">
-        <v>0.75</v>
+      <c r="Y127" s="10" t="n">
+        <v>1.5</v>
       </c>
       <c r="Z127" s="8" t="n"/>
     </row>
@@ -9329,10 +9297,10 @@
         <v>1</v>
       </c>
       <c r="H129" s="22" t="n">
+        <v>352500</v>
+      </c>
+      <c r="I129" s="8" t="n">
         <v>120000</v>
-      </c>
-      <c r="I129" s="8" t="n">
-        <v>352500</v>
       </c>
       <c r="J129" s="8" t="n">
         <v>21000</v>
@@ -9370,7 +9338,7 @@
         <v>1952</v>
       </c>
       <c r="Y129" s="13" t="n">
-        <v>0.6830601092896176</v>
+        <v>0.2325311010347634</v>
       </c>
       <c r="Z129" s="8" t="n">
         <v>3.9032006245121</v>
@@ -9405,10 +9373,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="22" t="n">
+        <v>57500</v>
+      </c>
+      <c r="I130" s="8" t="n">
         <v>120000</v>
-      </c>
-      <c r="I130" s="8" t="n">
-        <v>57500</v>
       </c>
       <c r="J130" s="8" t="n">
         <v>22500</v>
@@ -9445,8 +9413,8 @@
       <c r="X130" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="Y130" s="13" t="n">
-        <v>0.75</v>
+      <c r="Y130" s="10" t="n">
+        <v>1.565217391304348</v>
       </c>
       <c r="Z130" s="8" t="n">
         <v>4</v>
@@ -9477,10 +9445,10 @@
         <v>5</v>
       </c>
       <c r="H131" s="22" t="n">
+        <v>82500</v>
+      </c>
+      <c r="I131" s="8" t="n">
         <v>150000</v>
-      </c>
-      <c r="I131" s="8" t="n">
-        <v>82500</v>
       </c>
       <c r="J131" s="8" t="n">
         <v>32000</v>
@@ -9526,10 +9494,10 @@
       <c r="G132" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H132" s="22" t="n"/>
-      <c r="I132" s="8" t="n">
+      <c r="H132" s="22" t="n">
         <v>160000</v>
       </c>
+      <c r="I132" s="8" t="n"/>
       <c r="J132" s="8" t="n">
         <v>74000</v>
       </c>
@@ -9569,7 +9537,9 @@
       <c r="X132" s="10" t="n">
         <v>1689</v>
       </c>
-      <c r="Y132" s="12" t="n"/>
+      <c r="Y132" s="10" t="n">
+        <v>1.5625</v>
+      </c>
       <c r="Z132" s="8" t="n">
         <v>3.378378378378379</v>
       </c>
@@ -9599,10 +9569,10 @@
         <v>2</v>
       </c>
       <c r="H133" s="22" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I133" s="8" t="n">
         <v>400000</v>
-      </c>
-      <c r="I133" s="8" t="n">
-        <v>300000</v>
       </c>
       <c r="J133" s="8" t="n">
         <v>86000</v>
@@ -9634,7 +9604,7 @@
         <v>2712</v>
       </c>
       <c r="Y133" s="10" t="n">
-        <v>1.166</v>
+        <v>1.554666666666667</v>
       </c>
       <c r="Z133" s="8" t="n">
         <v>5.423255813953489</v>
@@ -9643,7 +9613,7 @@
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="19" t="inlineStr">
         <is>
-          <t>Кингстоны — 5 позиций, с ценой 2  наша цена 1 591-1 862 руб/кг  предложения 2 045-3 191</t>
+          <t>Кингстоны — 5 позиций, с ценой 2  наша цена по договору 1 579-2 128 руб/кг  предложения 2 045-3 191</t>
         </is>
       </c>
       <c r="B134" s="19" t="n"/>
@@ -9757,10 +9727,10 @@
         <v>2</v>
       </c>
       <c r="H136" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I136" s="8" t="n">
         <v>17500</v>
-      </c>
-      <c r="I136" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J136" s="8" t="n">
         <v>5500</v>
@@ -9798,7 +9768,7 @@
         <v>2045</v>
       </c>
       <c r="Y136" s="10" t="n">
-        <v>1.285714285714286</v>
+        <v>1.125</v>
       </c>
       <c r="Z136" s="8" t="n">
         <v>4.090909090909091</v>
@@ -9829,10 +9799,10 @@
         <v>1</v>
       </c>
       <c r="H137" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I137" s="8" t="n">
         <v>17500</v>
-      </c>
-      <c r="I137" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="J137" s="8" t="n">
         <v>4700</v>
@@ -9870,7 +9840,7 @@
         <v>3191</v>
       </c>
       <c r="Y137" s="10" t="n">
-        <v>1.714285714285714</v>
+        <v>1.5</v>
       </c>
       <c r="Z137" s="8" t="n">
         <v>6.382978723404255</v>
@@ -9905,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="H138" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I138" s="8" t="n">
         <v>32000</v>
-      </c>
-      <c r="I138" s="8" t="n">
-        <v>30000</v>
       </c>
       <c r="J138" s="8" t="n">
         <v>9500</v>
@@ -9959,10 +9929,10 @@
         <v>1</v>
       </c>
       <c r="H139" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I139" s="8" t="n">
         <v>32000</v>
-      </c>
-      <c r="I139" s="8" t="n">
-        <v>30000</v>
       </c>
       <c r="J139" s="8" t="n">
         <v>9500</v>
@@ -10419,7 +10389,7 @@
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="19" t="inlineStr">
         <is>
-          <t>Колонка смотровая — 2 позиции, с ценой 1  наша цена 909-4 000 руб/кг  предложения 1 364-1 364</t>
+          <t>Колонка смотровая — 2 позиции, с ценой 1  наша цена по договору 1 818-1 818 руб/кг  предложения 1 364-1 364</t>
         </is>
       </c>
       <c r="B149" s="19" t="n"/>
@@ -10476,10 +10446,10 @@
       <c r="G150" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H150" s="22" t="n">
+      <c r="H150" s="22" t="n"/>
+      <c r="I150" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="I150" s="8" t="n"/>
       <c r="J150" s="8" t="n">
         <v>750</v>
       </c>
@@ -10531,10 +10501,10 @@
         <v>12</v>
       </c>
       <c r="H151" s="22" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I151" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I151" s="8" t="n">
-        <v>12000</v>
       </c>
       <c r="J151" s="8" t="n">
         <v>3300</v>
@@ -10571,8 +10541,8 @@
       <c r="X151" s="10" t="n">
         <v>1364</v>
       </c>
-      <c r="Y151" s="10" t="n">
-        <v>1.5</v>
+      <c r="Y151" s="13" t="n">
+        <v>0.75</v>
       </c>
       <c r="Z151" s="8" t="n">
         <v>2.727272727272727</v>
@@ -10581,7 +10551,7 @@
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="19" t="inlineStr">
         <is>
-          <t>Захлопки — 6 позиций, с ценой 2  наша цена 1 187-2 381 руб/кг  предложения 2 232-3 169</t>
+          <t>Захлопки — 6 позиций, с ценой 2  наша цена по договору 1 538-2 381 руб/кг  предложения 2 232-3 169</t>
         </is>
       </c>
       <c r="B152" s="19" t="n"/>
@@ -10698,10 +10668,10 @@
       <c r="G154" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H154" s="22" t="n">
+      <c r="H154" s="22" t="n"/>
+      <c r="I154" s="8" t="n">
         <v>25000</v>
       </c>
-      <c r="I154" s="8" t="n"/>
       <c r="J154" s="8" t="n">
         <v>5600</v>
       </c>
@@ -10737,9 +10707,7 @@
       <c r="X154" s="10" t="n">
         <v>2232</v>
       </c>
-      <c r="Y154" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y154" s="12" t="n"/>
       <c r="Z154" s="8" t="n">
         <v>4.464285714285714</v>
       </c>
@@ -10772,10 +10740,10 @@
       <c r="G155" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H155" s="22" t="n">
+      <c r="H155" s="22" t="n"/>
+      <c r="I155" s="8" t="n">
         <v>40000</v>
       </c>
-      <c r="I155" s="8" t="n"/>
       <c r="J155" s="8" t="n">
         <v>16850</v>
       </c>
@@ -10977,7 +10945,7 @@
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="19" t="inlineStr">
         <is>
-          <t>Коробки клапанные — 5 позиций, с ценой 5  наша цена 924-1 167 руб/кг  предложения 1 386-2 195</t>
+          <t>Коробки клапанные — 5 позиций, с ценой 5  наша цена по договору 735-884 руб/кг  предложения 1 386-2 195</t>
         </is>
       </c>
       <c r="B159" s="19" t="n"/>
@@ -11031,10 +10999,10 @@
         <v>2</v>
       </c>
       <c r="H160" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I160" s="8" t="n">
         <v>35000</v>
-      </c>
-      <c r="I160" s="8" t="n">
-        <v>25000</v>
       </c>
       <c r="J160" s="8" t="n">
         <v>15000</v>
@@ -11078,7 +11046,7 @@
         <v>2000</v>
       </c>
       <c r="Y160" s="10" t="n">
-        <v>1.714285714285714</v>
+        <v>2.4</v>
       </c>
       <c r="Z160" s="8" t="n">
         <v>4</v>
@@ -11108,10 +11076,10 @@
       <c r="G161" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H161" s="22" t="n"/>
-      <c r="I161" s="8" t="n">
+      <c r="H161" s="22" t="n">
         <v>32500</v>
       </c>
+      <c r="I161" s="8" t="n"/>
       <c r="J161" s="8" t="n">
         <v>20500</v>
       </c>
@@ -11151,7 +11119,9 @@
       <c r="X161" s="10" t="n">
         <v>2195</v>
       </c>
-      <c r="Y161" s="12" t="n"/>
+      <c r="Y161" s="10" t="n">
+        <v>2.769230769230769</v>
+      </c>
       <c r="Z161" s="8" t="n">
         <v>4.390243902439025</v>
       </c>
@@ -11181,10 +11151,10 @@
         <v>15</v>
       </c>
       <c r="H162" s="22" t="n">
+        <v>35000</v>
+      </c>
+      <c r="I162" s="8" t="n">
         <v>44000</v>
-      </c>
-      <c r="I162" s="8" t="n">
-        <v>35000</v>
       </c>
       <c r="J162" s="8" t="n">
         <v>23800</v>
@@ -11228,7 +11198,7 @@
         <v>1756</v>
       </c>
       <c r="Y162" s="10" t="n">
-        <v>1.9</v>
+        <v>2.388571428571429</v>
       </c>
       <c r="Z162" s="8" t="n">
         <v>3.512605042016807</v>
@@ -11258,10 +11228,10 @@
       <c r="G163" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H163" s="22" t="n"/>
-      <c r="I163" s="8" t="n">
+      <c r="H163" s="22" t="n">
         <v>50000</v>
       </c>
+      <c r="I163" s="8" t="n"/>
       <c r="J163" s="8" t="n">
         <v>34000</v>
       </c>
@@ -11301,7 +11271,9 @@
       <c r="X163" s="10" t="n">
         <v>1386</v>
       </c>
-      <c r="Y163" s="12" t="n"/>
+      <c r="Y163" s="10" t="n">
+        <v>1.885245901639344</v>
+      </c>
       <c r="Z163" s="8" t="n">
         <v>2.772420443587271</v>
       </c>
@@ -11330,10 +11302,10 @@
       <c r="G164" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H164" s="22" t="n"/>
-      <c r="I164" s="8" t="n">
+      <c r="H164" s="22" t="n">
         <v>80000</v>
       </c>
+      <c r="I164" s="8" t="n"/>
       <c r="J164" s="8" t="n">
         <v>45250</v>
       </c>
@@ -11373,7 +11345,9 @@
       <c r="X164" s="10" t="n">
         <v>1459</v>
       </c>
-      <c r="Y164" s="12" t="n"/>
+      <c r="Y164" s="10" t="n">
+        <v>1.65</v>
+      </c>
       <c r="Z164" s="8" t="n">
         <v>2.917127071823205</v>
       </c>
@@ -11381,7 +11355,7 @@
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="19" t="inlineStr">
         <is>
-          <t>Краны — 9 позиций, с ценой 7  наша цена 1 920-5 000 руб/кг  предложения 1 134-7 500</t>
+          <t>Краны — 9 позиций, с ценой 7  наша цена по договору 1 585-4 167 руб/кг  предложения 1 134-7 500</t>
         </is>
       </c>
       <c r="B165" s="19" t="n"/>
@@ -11431,10 +11405,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I166" s="8" t="n">
         <v>7500</v>
-      </c>
-      <c r="I166" s="8" t="n">
-        <v>4000</v>
       </c>
       <c r="J166" s="8" t="n"/>
       <c r="K166" s="8" t="n"/>
@@ -11489,10 +11463,10 @@
         <v>6</v>
       </c>
       <c r="H167" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I167" s="8" t="n">
         <v>4000</v>
-      </c>
-      <c r="I167" s="8" t="n">
-        <v>5000</v>
       </c>
       <c r="J167" s="8" t="n">
         <v>600</v>
@@ -11530,7 +11504,7 @@
         <v>7500</v>
       </c>
       <c r="Y167" s="10" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Z167" s="8" t="n">
         <v>15</v>
@@ -11565,10 +11539,10 @@
         <v>7</v>
       </c>
       <c r="H168" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I168" s="8" t="n">
         <v>9000</v>
-      </c>
-      <c r="I168" s="8" t="n">
-        <v>5000</v>
       </c>
       <c r="J168" s="8" t="n">
         <v>1400</v>
@@ -11625,10 +11599,10 @@
         <v>40</v>
       </c>
       <c r="H169" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I169" s="8" t="n">
         <v>9000</v>
-      </c>
-      <c r="I169" s="8" t="n">
-        <v>6000</v>
       </c>
       <c r="J169" s="8" t="n">
         <v>900</v>
@@ -11665,8 +11639,8 @@
       <c r="X169" s="10" t="n">
         <v>4444</v>
       </c>
-      <c r="Y169" s="13" t="n">
-        <v>0.8888888888888888</v>
+      <c r="Y169" s="10" t="n">
+        <v>1.333333333333333</v>
       </c>
       <c r="Z169" s="8" t="n">
         <v>8.888888888888889</v>
@@ -11700,10 +11674,10 @@
       <c r="G170" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H170" s="22" t="n">
+      <c r="H170" s="22" t="n"/>
+      <c r="I170" s="8" t="n">
         <v>9600</v>
       </c>
-      <c r="I170" s="8" t="n"/>
       <c r="J170" s="8" t="n">
         <v>2500</v>
       </c>
@@ -11739,9 +11713,7 @@
       <c r="X170" s="10" t="n">
         <v>3200</v>
       </c>
-      <c r="Y170" s="10" t="n">
-        <v>1.666666666666667</v>
-      </c>
+      <c r="Y170" s="12" t="n"/>
       <c r="Z170" s="8" t="n">
         <v>6.4</v>
       </c>
@@ -11775,10 +11747,10 @@
         <v>2</v>
       </c>
       <c r="H171" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I171" s="8" t="n">
         <v>14400</v>
-      </c>
-      <c r="I171" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J171" s="8" t="n">
         <v>2050</v>
@@ -11820,7 +11792,7 @@
         <v>3512</v>
       </c>
       <c r="Y171" s="10" t="n">
-        <v>1</v>
+        <v>2.215384615384616</v>
       </c>
       <c r="Z171" s="8" t="n">
         <v>7.024390243902439</v>
@@ -11855,10 +11827,10 @@
         <v>1</v>
       </c>
       <c r="H172" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I172" s="8" t="n">
         <v>14400</v>
-      </c>
-      <c r="I172" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="J172" s="8" t="n">
         <v>2050</v>
@@ -11895,8 +11867,8 @@
       <c r="X172" s="10" t="n">
         <v>2341</v>
       </c>
-      <c r="Y172" s="13" t="n">
-        <v>0.6666666666666666</v>
+      <c r="Y172" s="10" t="n">
+        <v>1.476923076923077</v>
       </c>
       <c r="Z172" s="8" t="n">
         <v>4.682926829268292</v>
@@ -12277,7 +12249,7 @@
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="19" t="inlineStr">
         <is>
-          <t>Пусковые клапаны — 2 позиции, с ценой 0</t>
+          <t>Пусковые клапаны — 2 позиции, с ценой 0  наша цена по договору 3 409-4 464 руб/кг</t>
         </is>
       </c>
       <c r="B180" s="19" t="n"/>
@@ -12334,10 +12306,10 @@
       <c r="G181" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H181" s="22" t="n"/>
-      <c r="I181" s="8" t="n">
+      <c r="H181" s="22" t="n">
         <v>25000</v>
       </c>
+      <c r="I181" s="8" t="n"/>
       <c r="J181" s="8" t="n">
         <v>2800</v>
       </c>
@@ -12386,10 +12358,10 @@
       <c r="G182" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H182" s="22" t="n"/>
-      <c r="I182" s="8" t="n">
+      <c r="H182" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="I182" s="8" t="n"/>
       <c r="J182" s="8" t="n">
         <v>4400</v>
       </c>
@@ -12413,7 +12385,7 @@
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="19" t="inlineStr">
         <is>
-          <t>Редукционные клапаны — 3 позиции, с ценой 0  наша цена 800-800 руб/кг</t>
+          <t>Редукционные клапаны — 3 позиции, с ценой 0  наша цена по договору 1 296-2 000 руб/кг</t>
         </is>
       </c>
       <c r="B183" s="19" t="n"/>
@@ -12471,10 +12443,10 @@
         <v>1</v>
       </c>
       <c r="H184" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I184" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I184" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="J184" s="8" t="n">
         <v>68</v>
@@ -12525,10 +12497,10 @@
         <v>1</v>
       </c>
       <c r="H185" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I185" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="I185" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="J185" s="8" t="n">
         <v>68</v>
@@ -12578,10 +12550,10 @@
       <c r="G186" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H186" s="22" t="n"/>
-      <c r="I186" s="8" t="n">
+      <c r="H186" s="22" t="n">
         <v>35000</v>
       </c>
+      <c r="I186" s="8" t="n"/>
       <c r="J186" s="8" t="n">
         <v>243</v>
       </c>
@@ -12605,7 +12577,7 @@
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="19" t="inlineStr">
         <is>
-          <t>Паровые клапаны — 1 позиция, с ценой 0</t>
+          <t>Паровые клапаны — 1 позиция, с ценой 0  наша цена по договору 1 687-1 687 руб/кг</t>
         </is>
       </c>
       <c r="B187" s="19" t="n"/>
@@ -12662,10 +12634,10 @@
       <c r="G188" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H188" s="22" t="n"/>
-      <c r="I188" s="8" t="n">
+      <c r="H188" s="22" t="n">
         <v>55000</v>
       </c>
+      <c r="I188" s="8" t="n"/>
       <c r="J188" s="8" t="n">
         <v>293</v>
       </c>
@@ -12689,7 +12661,7 @@
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="19" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны — 3 позиции, с ценой 1  предложения 1 034-1 034</t>
+          <t>Электромагнитные клапаны — 3 позиции, с ценой 1  наша цена по договору 2 155-2 155 руб/кг  предложения 1 034-1 034</t>
         </is>
       </c>
       <c r="B189" s="19" t="n"/>
@@ -12746,10 +12718,10 @@
       <c r="G190" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H190" s="22" t="n"/>
-      <c r="I190" s="8" t="n">
+      <c r="H190" s="22" t="n">
         <v>25000</v>
       </c>
+      <c r="I190" s="8" t="n"/>
       <c r="J190" s="8" t="n">
         <v>5800</v>
       </c>
@@ -12785,7 +12757,9 @@
       <c r="X190" s="10" t="n">
         <v>1034</v>
       </c>
-      <c r="Y190" s="12" t="n"/>
+      <c r="Y190" s="13" t="n">
+        <v>0.48</v>
+      </c>
       <c r="Z190" s="8" t="n">
         <v>2.068965517241379</v>
       </c>
@@ -12879,7 +12853,7 @@
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="19" t="inlineStr">
         <is>
-          <t>Педальные клапаны — 2 позиции, с ценой 2  наша цена 2 273-2 273 руб/кг  предложения 3 273-4 000</t>
+          <t>Педальные клапаны — 2 позиции, с ценой 2  наша цена по договору 2 727-2 727 руб/кг  предложения 3 273-4 000</t>
         </is>
       </c>
       <c r="B193" s="19" t="n"/>
@@ -12937,10 +12911,10 @@
         <v>1</v>
       </c>
       <c r="H194" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I194" s="8" t="n">
         <v>12500</v>
-      </c>
-      <c r="I194" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="J194" s="8" t="n">
         <v>2750</v>
@@ -12978,7 +12952,7 @@
         <v>4000</v>
       </c>
       <c r="Y194" s="10" t="n">
-        <v>1.76</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="Z194" s="8" t="n">
         <v>8</v>
@@ -13013,10 +12987,10 @@
         <v>62</v>
       </c>
       <c r="H195" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I195" s="8" t="n">
         <v>12500</v>
-      </c>
-      <c r="I195" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="J195" s="8" t="n">
         <v>2750</v>
@@ -13048,7 +13022,7 @@
         <v>3273</v>
       </c>
       <c r="Y195" s="10" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="Z195" s="8" t="n">
         <v>6.545454545454546</v>
@@ -13057,7 +13031,7 @@
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="19" t="inlineStr">
         <is>
-          <t>Эжекторы — 1 позиция, с ценой 1  наша цена 6 250-6 250 руб/кг  предложения 7 500-7 500</t>
+          <t>Эжекторы — 1 позиция, с ценой 1  предложения 7 500-7 500</t>
         </is>
       </c>
       <c r="B196" s="19" t="n"/>
@@ -13108,10 +13082,10 @@
       <c r="G197" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H197" s="22" t="n">
+      <c r="H197" s="22" t="n"/>
+      <c r="I197" s="8" t="n">
         <v>25000</v>
       </c>
-      <c r="I197" s="8" t="n"/>
       <c r="J197" s="8" t="n">
         <v>2000</v>
       </c>
@@ -13141,9 +13115,7 @@
       <c r="X197" s="10" t="n">
         <v>7500</v>
       </c>
-      <c r="Y197" s="10" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="Y197" s="12" t="n"/>
       <c r="Z197" s="8" t="n">
         <v>15</v>
       </c>
@@ -13151,7 +13123,7 @@
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="19" t="inlineStr">
         <is>
-          <t>Без описания — уточнить — 3 позиции, с ценой 1  наша цена 2 043-3 750 руб/кг  предложения 2 043-2 043</t>
+          <t>Без описания — уточнить — 3 позиции, с ценой 1  предложения 2 043-2 043</t>
         </is>
       </c>
       <c r="B198" s="19" t="n"/>
@@ -13208,10 +13180,10 @@
       <c r="G199" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H199" s="22" t="n">
+      <c r="H199" s="22" t="n"/>
+      <c r="I199" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="I199" s="8" t="n"/>
       <c r="J199" s="8" t="n">
         <v>1200</v>
       </c>
@@ -13260,10 +13232,10 @@
       <c r="G200" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H200" s="22" t="n">
+      <c r="H200" s="22" t="n"/>
+      <c r="I200" s="8" t="n">
         <v>9600</v>
       </c>
-      <c r="I200" s="8" t="n"/>
       <c r="J200" s="8" t="n">
         <v>2350</v>
       </c>
@@ -13299,9 +13271,7 @@
       <c r="X200" s="10" t="n">
         <v>2043</v>
       </c>
-      <c r="Y200" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y200" s="12" t="n"/>
       <c r="Z200" s="8" t="n">
         <v>4.085106382978723</v>
       </c>
@@ -13393,7 +13363,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>87 позиций  2 815 кг. Разложены по тем же группам. Первой колонкой наша цена продажи: по многим она есть  и рассылать можно сразу с ней.</t>
+          <t>87 позиций  2 815 кг. Разложены по тем же группам. Первой колонкой наша продажная цена по договору  рядом справочная цена по учету склада.</t>
         </is>
       </c>
     </row>
@@ -13440,12 +13410,12 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>НАША ЦЕНА продажи</t>
+          <t>НАША ЦЕНА продажи по договору</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Наша цена по договору</t>
+          <t>Справочно: цена по учету склада</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -13508,10 +13478,10 @@
       <c r="H6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n">
         <v>3500</v>
       </c>
@@ -13553,10 +13523,10 @@
         <v>4</v>
       </c>
       <c r="I7" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J7" s="8" t="n">
         <v>4000</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>3000</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>4500</v>
@@ -13599,10 +13569,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J8" s="8" t="n">
         <v>7500</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>5000</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>6000</v>
@@ -13644,10 +13614,10 @@
       <c r="H9" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="J9" s="8" t="n"/>
       <c r="K9" s="8" t="n">
         <v>6000</v>
       </c>
@@ -13688,10 +13658,10 @@
       <c r="H10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n">
         <v>5000</v>
       </c>
@@ -13816,10 +13786,10 @@
       <c r="H13" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n">
         <v>5000</v>
       </c>
@@ -13861,10 +13831,10 @@
         <v>4</v>
       </c>
       <c r="I14" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="8" t="n">
         <v>4800</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>10000</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>6000</v>
@@ -13907,10 +13877,10 @@
         <v>2</v>
       </c>
       <c r="I15" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J15" s="8" t="n">
         <v>3000</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>4000</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>5000</v>
@@ -13952,10 +13922,10 @@
       <c r="H16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="8" t="n">
         <v>7500</v>
       </c>
-      <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n">
         <v>8750</v>
       </c>
@@ -14122,10 +14092,10 @@
       <c r="H20" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="24" t="n"/>
+      <c r="J20" s="8" t="n">
         <v>10500</v>
       </c>
-      <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n">
         <v>7500</v>
       </c>
@@ -14167,10 +14137,10 @@
         <v>11</v>
       </c>
       <c r="I21" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="J21" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>6500</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>9600</v>
@@ -14213,10 +14183,10 @@
         <v>5</v>
       </c>
       <c r="I22" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J22" s="8" t="n">
         <v>10000</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="7" t="inlineStr"/>
@@ -14251,10 +14221,10 @@
         <v>8</v>
       </c>
       <c r="I23" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J23" s="8" t="n">
         <v>4000</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>3000</v>
       </c>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="7" t="inlineStr"/>
@@ -14262,7 +14232,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>Штуцерная проходная — 6 позиций  26 кг  наша цена есть у 4</t>
+          <t>Штуцерная проходная — 6 позиций  26 кг  наша цена есть у 5</t>
         </is>
       </c>
       <c r="B24" s="19" t="n"/>
@@ -14308,10 +14278,10 @@
       <c r="H25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="24" t="n"/>
-      <c r="J25" s="8" t="n">
+      <c r="I25" s="22" t="n">
         <v>4000</v>
       </c>
+      <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n">
         <v>6500</v>
       </c>
@@ -14386,10 +14356,10 @@
       <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n">
         <v>6000</v>
       </c>
@@ -14430,10 +14400,10 @@
       <c r="H28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="8" t="n">
         <v>7500</v>
       </c>
-      <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n">
         <v>6000</v>
       </c>
@@ -14474,10 +14444,10 @@
       <c r="H29" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n">
         <v>4500</v>
       </c>
@@ -14510,10 +14480,10 @@
       <c r="H30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="22" t="n">
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n">
         <v>9600</v>
       </c>
@@ -14526,7 +14496,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>Штуцерная  угол или проход не указан — 8 позиций  74 кг  наша цена есть у 5</t>
+          <t>Штуцерная  угол или проход не указан — 8 позиций  74 кг  наша цена есть у 8</t>
         </is>
       </c>
       <c r="B31" s="19" t="n"/>
@@ -14573,10 +14543,10 @@
         <v>4</v>
       </c>
       <c r="I32" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J32" s="8" t="n">
         <v>4500</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="K32" s="8" t="n"/>
       <c r="L32" s="7" t="inlineStr"/>
@@ -14612,10 +14582,10 @@
       <c r="H33" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="22" t="n">
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="8" t="n">
         <v>4500</v>
       </c>
-      <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n">
         <v>6000</v>
       </c>
@@ -14657,10 +14627,10 @@
         <v>1</v>
       </c>
       <c r="I34" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J34" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="J34" s="8" t="n">
-        <v>3500</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>4500</v>
@@ -14703,10 +14673,10 @@
         <v>1</v>
       </c>
       <c r="I35" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J35" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>3500</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>5625</v>
@@ -14748,10 +14718,10 @@
       <c r="H36" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I36" s="24" t="n"/>
-      <c r="J36" s="8" t="n">
+      <c r="I36" s="22" t="n">
         <v>17500</v>
       </c>
+      <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="7" t="inlineStr"/>
     </row>
@@ -14787,10 +14757,10 @@
         <v>2</v>
       </c>
       <c r="I37" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J37" s="8" t="n">
         <v>10000</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="7" t="inlineStr"/>
@@ -14826,10 +14796,10 @@
       <c r="H38" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="I38" s="24" t="n"/>
-      <c r="J38" s="8" t="n">
+      <c r="I38" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="7" t="inlineStr"/>
     </row>
@@ -14864,10 +14834,10 @@
       <c r="H39" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="I39" s="24" t="n"/>
-      <c r="J39" s="8" t="n">
+      <c r="I39" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="7" t="inlineStr"/>
     </row>
@@ -14921,10 +14891,10 @@
         <v>72</v>
       </c>
       <c r="I41" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J41" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="7" t="inlineStr"/>
@@ -14961,10 +14931,10 @@
         <v>6</v>
       </c>
       <c r="I42" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J42" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="J42" s="8" t="n">
-        <v>20000</v>
       </c>
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="7" t="inlineStr"/>
@@ -15080,10 +15050,10 @@
       <c r="H45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="22" t="n">
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="8" t="n">
         <v>22500</v>
       </c>
-      <c r="J45" s="8" t="n"/>
       <c r="K45" s="8" t="n">
         <v>20000</v>
       </c>
@@ -15121,10 +15091,10 @@
         <v>16</v>
       </c>
       <c r="I46" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J46" s="8" t="n">
         <v>27000</v>
-      </c>
-      <c r="J46" s="8" t="n">
-        <v>25000</v>
       </c>
       <c r="K46" s="8" t="n">
         <v>24500</v>
@@ -15163,10 +15133,10 @@
         <v>16</v>
       </c>
       <c r="I47" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J47" s="8" t="n">
         <v>27000</v>
-      </c>
-      <c r="J47" s="8" t="n">
-        <v>25000</v>
       </c>
       <c r="K47" s="8" t="n">
         <v>25150</v>
@@ -15243,10 +15213,10 @@
         <v>0</v>
       </c>
       <c r="I49" s="22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J49" s="8" t="n">
         <v>80000</v>
-      </c>
-      <c r="J49" s="8" t="n">
-        <v>50000</v>
       </c>
       <c r="K49" s="8" t="n">
         <v>60000</v>
@@ -15260,7 +15230,7 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>Фланцевая проходная — 7 позиций  612 кг  наша цена есть у 1</t>
+          <t>Фланцевая проходная — 7 позиций  612 кг  наша цена есть у 4</t>
         </is>
       </c>
       <c r="B50" s="19" t="n"/>
@@ -15348,10 +15318,10 @@
       <c r="H52" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="I52" s="24" t="n"/>
-      <c r="J52" s="8" t="n">
+      <c r="I52" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="J52" s="8" t="n"/>
       <c r="K52" s="8" t="n">
         <v>23000</v>
       </c>
@@ -15434,10 +15404,10 @@
       <c r="H54" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I54" s="24" t="n"/>
-      <c r="J54" s="8" t="n">
+      <c r="I54" s="22" t="n">
         <v>47500</v>
       </c>
+      <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n">
         <v>36000</v>
       </c>
@@ -15512,10 +15482,10 @@
       <c r="H56" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="I56" s="24" t="n"/>
-      <c r="J56" s="8" t="n">
+      <c r="I56" s="22" t="n">
         <v>55000</v>
       </c>
+      <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n">
         <v>37500</v>
       </c>
@@ -15552,10 +15522,10 @@
       <c r="H57" s="8" t="n">
         <v>330</v>
       </c>
-      <c r="I57" s="22" t="n">
+      <c r="I57" s="24" t="n"/>
+      <c r="J57" s="8" t="n">
         <v>150000</v>
       </c>
-      <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="7" t="inlineStr"/>
     </row>
@@ -15669,10 +15639,10 @@
         <v>228</v>
       </c>
       <c r="I61" s="22" t="n">
+        <v>275000</v>
+      </c>
+      <c r="J61" s="8" t="n">
         <v>300000</v>
-      </c>
-      <c r="J61" s="8" t="n">
-        <v>275000</v>
       </c>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="7" t="inlineStr"/>
@@ -15839,10 +15809,10 @@
         <v>320</v>
       </c>
       <c r="I66" s="22" t="n">
+        <v>82500</v>
+      </c>
+      <c r="J66" s="8" t="n">
         <v>150000</v>
-      </c>
-      <c r="J66" s="8" t="n">
-        <v>82500</v>
       </c>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="7" t="inlineStr"/>
@@ -15939,10 +15909,10 @@
         <v>38</v>
       </c>
       <c r="I69" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J69" s="8" t="n">
         <v>32000</v>
-      </c>
-      <c r="J69" s="8" t="n">
-        <v>30000</v>
       </c>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="7" t="inlineStr"/>
@@ -15979,10 +15949,10 @@
         <v>19</v>
       </c>
       <c r="I70" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J70" s="8" t="n">
         <v>32000</v>
-      </c>
-      <c r="J70" s="8" t="n">
-        <v>30000</v>
       </c>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="7" t="inlineStr"/>
@@ -16342,10 +16312,10 @@
       <c r="H81" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I81" s="22" t="n">
+      <c r="I81" s="24" t="n"/>
+      <c r="J81" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="J81" s="8" t="n"/>
       <c r="K81" s="8" t="n">
         <v>9000</v>
       </c>
@@ -16450,10 +16420,10 @@
       <c r="H84" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="I84" s="22" t="n">
+      <c r="I84" s="24" t="n"/>
+      <c r="J84" s="8" t="n">
         <v>40000</v>
       </c>
-      <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="7" t="inlineStr"/>
     </row>
@@ -16579,10 +16549,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J88" s="8" t="n">
         <v>7500</v>
-      </c>
-      <c r="J88" s="8" t="n">
-        <v>4000</v>
       </c>
       <c r="K88" s="8" t="n">
         <v>6500</v>
@@ -16625,10 +16595,10 @@
         <v>20</v>
       </c>
       <c r="I89" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J89" s="8" t="n">
         <v>9000</v>
-      </c>
-      <c r="J89" s="8" t="n">
-        <v>5000</v>
       </c>
       <c r="K89" s="8" t="n">
         <v>6000</v>
@@ -16804,7 +16774,7 @@
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>Пусковые клапаны — 2 позиции  110 кг  наша цена есть у 0</t>
+          <t>Пусковые клапаны — 2 позиции  110 кг  наша цена есть у 2</t>
         </is>
       </c>
       <c r="B95" s="19" t="n"/>
@@ -16850,10 +16820,10 @@
       <c r="H96" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="I96" s="24" t="n"/>
-      <c r="J96" s="8" t="n">
+      <c r="I96" s="22" t="n">
         <v>25000</v>
       </c>
+      <c r="J96" s="8" t="n"/>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="7" t="inlineStr"/>
     </row>
@@ -16888,17 +16858,17 @@
       <c r="H97" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="I97" s="24" t="n"/>
-      <c r="J97" s="8" t="n">
+      <c r="I97" s="22" t="n">
         <v>30000</v>
       </c>
+      <c r="J97" s="8" t="n"/>
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="7" t="inlineStr"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="19" t="inlineStr">
         <is>
-          <t>Редукционные клапаны — 3 позиции  258 кг  наша цена есть у 2</t>
+          <t>Редукционные клапаны — 3 позиции  258 кг  наша цена есть у 3</t>
         </is>
       </c>
       <c r="B98" s="19" t="n"/>
@@ -16945,10 +16915,10 @@
         <v>8</v>
       </c>
       <c r="I99" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J99" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="J99" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="7" t="inlineStr"/>
@@ -16985,10 +16955,10 @@
         <v>8</v>
       </c>
       <c r="I100" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J100" s="8" t="n">
         <v>6000</v>
-      </c>
-      <c r="J100" s="8" t="n">
-        <v>15000</v>
       </c>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="7" t="inlineStr"/>
@@ -17024,17 +16994,17 @@
       <c r="H101" s="8" t="n">
         <v>243</v>
       </c>
-      <c r="I101" s="24" t="n"/>
-      <c r="J101" s="8" t="n">
+      <c r="I101" s="22" t="n">
         <v>35000</v>
       </c>
+      <c r="J101" s="8" t="n"/>
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="7" t="inlineStr"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="19" t="inlineStr">
         <is>
-          <t>Паровые клапаны — 1 позиция  33 кг  наша цена есть у 0</t>
+          <t>Паровые клапаны — 1 позиция  33 кг  наша цена есть у 1</t>
         </is>
       </c>
       <c r="B102" s="19" t="n"/>
@@ -17080,10 +17050,10 @@
       <c r="H103" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="I103" s="24" t="n"/>
-      <c r="J103" s="8" t="n">
+      <c r="I103" s="22" t="n">
         <v>55000</v>
       </c>
+      <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="7" t="inlineStr"/>
     </row>
@@ -17214,10 +17184,10 @@
       <c r="H108" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I108" s="22" t="n">
+      <c r="I108" s="24" t="n"/>
+      <c r="J108" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="J108" s="8" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="7" t="inlineStr"/>
     </row>
@@ -17328,7 +17298,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>НАША ЦЕНА, руб за кг</t>
+          <t>НАША ЦЕНА по договору, руб за кг</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -17391,7 +17361,7 @@
         <v>500</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>2909</v>
+        <v>2105</v>
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
@@ -17451,7 +17421,7 @@
         <v>500</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>2857</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
@@ -17511,7 +17481,7 @@
         <v>500</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>6429</v>
+        <v>5000</v>
       </c>
       <c r="G7" s="27" t="inlineStr">
         <is>
@@ -17571,7 +17541,7 @@
         <v>500</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>1688</v>
+        <v>1562</v>
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
@@ -17631,7 +17601,7 @@
         <v>500</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>1364</v>
+        <v>1458</v>
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
@@ -17690,8 +17660,10 @@
       <c r="E10" s="25" t="n">
         <v>500</v>
       </c>
-      <c r="F10" s="26" t="n">
-        <v>1556</v>
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
@@ -17751,7 +17723,7 @@
         <v>500</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>1316</v>
+        <v>1120</v>
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
@@ -17811,7 +17783,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>2667</v>
+        <v>1289</v>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
@@ -17871,7 +17843,7 @@
         <v>500</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>1684</v>
+        <v>1818</v>
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
@@ -17995,7 +17967,7 @@
         <v>500</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>4000</v>
+        <v>1818</v>
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
@@ -18115,7 +18087,7 @@
         <v>500</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>1167</v>
+        <v>793</v>
       </c>
       <c r="G17" s="27" t="inlineStr">
         <is>
@@ -18175,7 +18147,7 @@
         <v>500</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>3512</v>
+        <v>1786</v>
       </c>
       <c r="G18" s="27" t="inlineStr">
         <is>
@@ -18298,10 +18270,8 @@
       <c r="E20" s="25" t="n">
         <v>500</v>
       </c>
-      <c r="F20" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F20" s="26" t="n">
+        <v>4464</v>
       </c>
       <c r="G20" s="28" t="inlineStr">
         <is>
@@ -18363,7 +18333,7 @@
         <v>9</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
@@ -18424,10 +18394,8 @@
       <c r="E22" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F22" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F22" s="26" t="n">
+        <v>1687</v>
       </c>
       <c r="G22" s="28" t="inlineStr">
         <is>
@@ -18488,10 +18456,8 @@
       <c r="E23" s="25" t="n">
         <v>500</v>
       </c>
-      <c r="F23" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F23" s="26" t="n">
+        <v>2155</v>
       </c>
       <c r="G23" s="27" t="inlineStr">
         <is>
@@ -18551,7 +18517,7 @@
         <v>500</v>
       </c>
       <c r="F24" s="26" t="n">
-        <v>2273</v>
+        <v>2727</v>
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
@@ -18612,8 +18578,10 @@
       <c r="E25" s="25" t="n">
         <v>500</v>
       </c>
-      <c r="F25" s="26" t="n">
-        <v>6250</v>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G25" s="27" t="inlineStr">
         <is>
@@ -18674,8 +18642,10 @@
       <c r="E26" s="25" t="n">
         <v>500</v>
       </c>
-      <c r="F26" s="26" t="n">
-        <v>3750</v>
+      <c r="F26" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G26" s="27" t="inlineStr">
         <is>

--- a/outputs/marine_equipment/Анализ_цен.xlsx
+++ b/outputs/marine_equipment/Анализ_цен.xlsx
@@ -3827,7 +3827,7 @@
         <v>798</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>3000</v>
@@ -3874,7 +3874,7 @@
         <v>15125</v>
       </c>
       <c r="Y41" s="10" t="n">
-        <v>4.5375</v>
+        <v>3.63</v>
       </c>
       <c r="Z41" s="8" t="n">
         <v>30.25</v>
@@ -5361,7 +5361,7 @@
         <v>18</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="I64" s="8" t="n">
         <v>6000</v>
@@ -5396,7 +5396,7 @@
         <v>8571</v>
       </c>
       <c r="Y64" s="10" t="n">
-        <v>1.714285714285714</v>
+        <v>1.5</v>
       </c>
       <c r="Z64" s="8" t="n">
         <v>17.14285714285714</v>
@@ -5431,7 +5431,7 @@
         <v>124</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="I65" s="8" t="n">
         <v>4500</v>
@@ -5482,7 +5482,7 @@
         <v>43857</v>
       </c>
       <c r="Y65" s="10" t="n">
-        <v>8.771428571428572</v>
+        <v>7.675</v>
       </c>
       <c r="Z65" s="8" t="n">
         <v>87.71428571428571</v>
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="I70" s="8" t="n"/>
       <c r="J70" s="8" t="n">
@@ -5801,7 +5801,7 @@
         <v>20</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n">
@@ -5834,7 +5834,7 @@
         <v>1745</v>
       </c>
       <c r="Y71" s="13" t="n">
-        <v>0.5485714285714286</v>
+        <v>0.48</v>
       </c>
       <c r="Z71" s="8" t="n">
         <v>3.490909090909091</v>
@@ -7095,7 +7095,7 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>Фланцевая проходная — 12 позиций, с ценой 5  наша цена по договору 1 196-8 571 руб/кг  предложения 1 222-2 373</t>
+          <t>Фланцевая проходная — 12 позиций, с ценой 5  наша цена по договору 1 196-10 000 руб/кг  предложения 1 222-2 373</t>
         </is>
       </c>
       <c r="B93" s="19" t="n"/>
@@ -7149,7 +7149,7 @@
         <v>51</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="I94" s="8" t="n">
         <v>22500</v>
@@ -7196,7 +7196,7 @@
         <v>2292</v>
       </c>
       <c r="Y94" s="10" t="n">
-        <v>1.571428571428571</v>
+        <v>1.375</v>
       </c>
       <c r="Z94" s="8" t="n">
         <v>4.583333333333333</v>
@@ -7287,7 +7287,7 @@
         <v>5</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="I96" s="8" t="n"/>
       <c r="J96" s="8" t="n"/>
@@ -7539,7 +7539,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="22" t="n">
-        <v>47500</v>
+        <v>55000</v>
       </c>
       <c r="I100" s="8" t="n"/>
       <c r="J100" s="8" t="n"/>
@@ -8335,7 +8335,7 @@
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="19" t="inlineStr">
         <is>
-          <t>Клинкеты — 10 позиций, с ценой 7  наша цена по договору 964-1 206 руб/кг  предложения 1 311-6 686</t>
+          <t>Клинкеты — 10 позиций, с ценой 7  наша цена по договору 1 023-1 316 руб/кг  предложения 1 311-6 686</t>
         </is>
       </c>
       <c r="B113" s="19" t="n"/>
@@ -8693,7 +8693,7 @@
         <v>15</v>
       </c>
       <c r="H119" s="22" t="n">
-        <v>87500</v>
+        <v>90000</v>
       </c>
       <c r="I119" s="8" t="n">
         <v>150000</v>
@@ -8740,7 +8740,7 @@
         <v>1705</v>
       </c>
       <c r="Y119" s="10" t="n">
-        <v>1.714285714285714</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Z119" s="8" t="n">
         <v>3.409090909090909</v>
@@ -8771,7 +8771,7 @@
         <v>19</v>
       </c>
       <c r="H120" s="22" t="n">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="I120" s="8" t="n">
         <v>200000</v>
@@ -8818,7 +8818,7 @@
         <v>1311</v>
       </c>
       <c r="Y120" s="10" t="n">
-        <v>1.17096018735363</v>
+        <v>1.092896174863388</v>
       </c>
       <c r="Z120" s="8" t="n">
         <v>2.622950819672131</v>
@@ -8915,7 +8915,7 @@
         <v>13</v>
       </c>
       <c r="H122" s="22" t="n">
-        <v>185000</v>
+        <v>200000</v>
       </c>
       <c r="I122" s="8" t="n">
         <v>250000</v>
@@ -8956,7 +8956,7 @@
         <v>3063</v>
       </c>
       <c r="Y122" s="10" t="n">
-        <v>3.178918918918919</v>
+        <v>2.9405</v>
       </c>
       <c r="Z122" s="8" t="n">
         <v>6.126041666666667</v>
@@ -8987,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="22" t="n">
-        <v>275000</v>
+        <v>300000</v>
       </c>
       <c r="I123" s="8" t="n">
         <v>300000</v>
@@ -9015,7 +9015,7 @@
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="19" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды — 9 позиций, с ценой 5  наша цена по договору 1 081-8 393 руб/кг  предложения 1 689-2 712</t>
+          <t>Фильтры забортной воды — 9 позиций, с ценой 5  наша цена по договору 1 149-1 744 руб/кг  предложения 1 689-2 712</t>
         </is>
       </c>
       <c r="B124" s="19" t="n"/>
@@ -9297,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="22" t="n">
-        <v>352500</v>
+        <v>55000</v>
       </c>
       <c r="I129" s="8" t="n">
         <v>120000</v>
@@ -9337,8 +9337,8 @@
       <c r="X129" s="10" t="n">
         <v>1952</v>
       </c>
-      <c r="Y129" s="13" t="n">
-        <v>0.2325311010347634</v>
+      <c r="Y129" s="10" t="n">
+        <v>1.490312965722802</v>
       </c>
       <c r="Z129" s="8" t="n">
         <v>3.9032006245121</v>
@@ -9373,7 +9373,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="22" t="n">
-        <v>57500</v>
+        <v>60000</v>
       </c>
       <c r="I130" s="8" t="n">
         <v>120000</v>
@@ -9414,7 +9414,7 @@
         <v>2000</v>
       </c>
       <c r="Y130" s="10" t="n">
-        <v>1.565217391304348</v>
+        <v>1.5</v>
       </c>
       <c r="Z130" s="8" t="n">
         <v>4</v>
@@ -9445,7 +9445,7 @@
         <v>5</v>
       </c>
       <c r="H131" s="22" t="n">
-        <v>82500</v>
+        <v>90000</v>
       </c>
       <c r="I131" s="8" t="n">
         <v>150000</v>
@@ -9495,7 +9495,7 @@
         <v>8</v>
       </c>
       <c r="H132" s="22" t="n">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="I132" s="8" t="n"/>
       <c r="J132" s="8" t="n">
@@ -9538,7 +9538,7 @@
         <v>1689</v>
       </c>
       <c r="Y132" s="10" t="n">
-        <v>1.5625</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="Z132" s="8" t="n">
         <v>3.378378378378379</v>
@@ -11077,7 +11077,7 @@
         <v>5</v>
       </c>
       <c r="H161" s="22" t="n">
-        <v>32500</v>
+        <v>35000</v>
       </c>
       <c r="I161" s="8" t="n"/>
       <c r="J161" s="8" t="n">
@@ -11120,7 +11120,7 @@
         <v>2195</v>
       </c>
       <c r="Y161" s="10" t="n">
-        <v>2.769230769230769</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="Z161" s="8" t="n">
         <v>4.390243902439025</v>
@@ -11229,7 +11229,7 @@
         <v>12</v>
       </c>
       <c r="H163" s="22" t="n">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="I163" s="8" t="n"/>
       <c r="J163" s="8" t="n">
@@ -11272,7 +11272,7 @@
         <v>1386</v>
       </c>
       <c r="Y163" s="10" t="n">
-        <v>1.885245901639344</v>
+        <v>1.713859910581222</v>
       </c>
       <c r="Z163" s="8" t="n">
         <v>2.772420443587271</v>
@@ -12577,7 +12577,7 @@
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="19" t="inlineStr">
         <is>
-          <t>Паровые клапаны — 1 позиция, с ценой 0  наша цена по договору 1 687-1 687 руб/кг</t>
+          <t>Паровые клапаны — 1 позиция, с ценой 0  наша цена по договору 1 840-1 840 руб/кг</t>
         </is>
       </c>
       <c r="B187" s="19" t="n"/>
@@ -12635,7 +12635,7 @@
         <v>1</v>
       </c>
       <c r="H188" s="22" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="I188" s="8" t="n"/>
       <c r="J188" s="8" t="n">
@@ -14719,7 +14719,7 @@
         <v>6</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
@@ -15319,7 +15319,7 @@
         <v>18</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="J52" s="8" t="n"/>
       <c r="K52" s="8" t="n">
@@ -15405,7 +15405,7 @@
         <v>10</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>47500</v>
+        <v>55000</v>
       </c>
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="8" t="n">
@@ -15639,7 +15639,7 @@
         <v>228</v>
       </c>
       <c r="I61" s="22" t="n">
-        <v>275000</v>
+        <v>300000</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>300000</v>
@@ -15809,7 +15809,7 @@
         <v>320</v>
       </c>
       <c r="I66" s="22" t="n">
-        <v>82500</v>
+        <v>90000</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>150000</v>
@@ -17051,7 +17051,7 @@
         <v>33</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
@@ -17481,7 +17481,7 @@
         <v>500</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>5000</v>
+        <v>5263</v>
       </c>
       <c r="G7" s="27" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>500</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>1458</v>
+        <v>1667</v>
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>500</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>1120</v>
+        <v>1200</v>
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>1289</v>
+        <v>1333</v>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>500</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="G17" s="27" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>9</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>1687</v>
+        <v>1840</v>
       </c>
       <c r="G22" s="28" t="inlineStr">
         <is>

--- a/outputs/marine_equipment/Анализ_цен.xlsx
+++ b/outputs/marine_equipment/Анализ_цен.xlsx
@@ -9297,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="22" t="n">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="I129" s="8" t="n">
         <v>120000</v>
@@ -9338,7 +9338,7 @@
         <v>1952</v>
       </c>
       <c r="Y129" s="10" t="n">
-        <v>1.490312965722802</v>
+        <v>1.261034047919294</v>
       </c>
       <c r="Z129" s="8" t="n">
         <v>3.9032006245121</v>
@@ -17783,7 +17783,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>1333</v>
+        <v>1406</v>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>

--- a/outputs/marine_equipment/Анализ_цен.xlsx
+++ b/outputs/marine_equipment/Анализ_цен.xlsx
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>9054247</v>
+        <v>9029340</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>— Лом держит нижнюю границу. Весь перечень этого файла в ломе — 9.1 млн руб, и ни одно предложение ниже лома не опускается: минимум 2.1 раза выше, медиана 5.6. Значит торговаться есть куда, но и пол понятен.</t>
+          <t>— Лом держит нижнюю границу. Весь перечень этого файла в ломе — 9.0 млн руб, и ни одно предложение ниже лома не опускается: минимум 2.1 раза выше, медиана 5.6. Значит торговаться есть куда, но и пол понятен.</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       <c r="H145" s="22" t="n"/>
       <c r="I145" s="8" t="n"/>
       <c r="J145" s="8" t="n">
-        <v>1450</v>
+        <v>276</v>
       </c>
       <c r="K145" s="8" t="n"/>
       <c r="L145" s="8" t="n"/>
@@ -10267,7 +10267,7 @@
       <c r="H146" s="22" t="n"/>
       <c r="I146" s="8" t="n"/>
       <c r="J146" s="8" t="n">
-        <v>1350</v>
+        <v>256</v>
       </c>
       <c r="K146" s="8" t="n"/>
       <c r="L146" s="8" t="n"/>
@@ -10317,7 +10317,7 @@
       <c r="H147" s="22" t="n"/>
       <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n">
-        <v>1900</v>
+        <v>361</v>
       </c>
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
@@ -10367,7 +10367,7 @@
       <c r="H148" s="22" t="n"/>
       <c r="I148" s="8" t="n"/>
       <c r="J148" s="8" t="n">
-        <v>2350</v>
+        <v>446</v>
       </c>
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>

--- a/outputs/marine_equipment/Анализ_цен.xlsx
+++ b/outputs/marine_equipment/Анализ_цен.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Цены по группам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Никто не оценил" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Матрица групп" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены по группам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Никто не оценил" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица групп" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Цены по группам'!$A$4:$Z$201</definedName>
@@ -12568,8 +12568,14 @@
       <c r="S186" s="8" t="n"/>
       <c r="T186" s="8" t="n"/>
       <c r="U186" s="12" t="n"/>
-      <c r="V186" s="8" t="n"/>
-      <c r="W186" s="8" t="inlineStr"/>
+      <c r="V186" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W186" s="8" t="inlineStr">
+        <is>
+          <t>по типу и диаметру</t>
+        </is>
+      </c>
       <c r="X186" s="12" t="n"/>
       <c r="Y186" s="12" t="n"/>
       <c r="Z186" s="8" t="n"/>
@@ -16998,8 +17004,14 @@
         <v>35000</v>
       </c>
       <c r="J101" s="8" t="n"/>
-      <c r="K101" s="8" t="n"/>
-      <c r="L101" s="7" t="inlineStr"/>
+      <c r="K101" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>по типу и диаметру</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="19" t="inlineStr">
@@ -18370,10 +18382,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N21" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N21" s="14" t="n">
+        <v>222</v>
       </c>
     </row>
     <row r="22">

--- a/outputs/marine_equipment/Анализ_цен.xlsx
+++ b/outputs/marine_equipment/Анализ_цен.xlsx
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="B37" s="15" t="n">
-        <v>600</v>
+        <v>745</v>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
     </row>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B38" s="15" t="n">
-        <v>500</v>
+        <v>635</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B39" s="15" t="n">
-        <v>900</v>
+        <v>945</v>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B40" s="15" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
     </row>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B41" s="15" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
     </row>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B42" s="15" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
     </row>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>9029340</v>
+        <v>13569089</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
     </row>
@@ -1326,7 +1326,7 @@
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>— Лом держит нижнюю границу. Весь перечень этого файла в ломе — 9.0 млн руб, и ни одно предложение ниже лома не опускается: минимум 2.1 раза выше, медиана 5.6. Значит торговаться есть куда, но и пол понятен.</t>
+          <t>— Лом держит нижнюю границу. Весь перечень этого файла в ломе — 13.6 млн руб, и ни одно предложение ниже лома не опускается: минимум 1.4 раза выше, медиана 3.8. Значит торговаться есть куда, но и пол понятен.</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
         <v>9000</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>760</v>
+        <v>1132</v>
       </c>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
@@ -1643,7 +1643,7 @@
         <v>4000</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="8" t="n"/>
@@ -1703,7 +1703,7 @@
         <v>7500</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>650</v>
+        <v>968</v>
       </c>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I9" s="8" t="n"/>
       <c r="J9" s="8" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="K9" s="23" t="n">
         <v>9000</v>
@@ -1799,7 +1799,7 @@
         <v>1.384615384615385</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>400</v>
+        <v>166.6666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -1835,7 +1835,7 @@
         <v>9000</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>2150</v>
+        <v>3204</v>
       </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
@@ -1893,7 +1893,7 @@
         <v>6000</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>2450</v>
+        <v>3651</v>
       </c>
       <c r="K11" s="23" t="n">
         <v>7500</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Y11" s="12" t="n"/>
       <c r="Z11" s="8" t="n">
-        <v>3.061224489795918</v>
+        <v>2.054513080399945</v>
       </c>
     </row>
     <row r="12">
@@ -1965,7 +1965,7 @@
         <v>6000</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>1000</v>
+        <v>1490</v>
       </c>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n"/>
@@ -2021,7 +2021,7 @@
       <c r="H13" s="22" t="n"/>
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n">
-        <v>1000</v>
+        <v>1490</v>
       </c>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
@@ -2077,7 +2077,7 @@
       <c r="H14" s="22" t="n"/>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n">
-        <v>1000</v>
+        <v>1490</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>6000</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Y14" s="12" t="n"/>
       <c r="Z14" s="8" t="n">
-        <v>21.7</v>
+        <v>14.56375838926174</v>
       </c>
     </row>
     <row r="15">
@@ -2153,7 +2153,7 @@
       <c r="H15" s="22" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n">
-        <v>1000</v>
+        <v>1490</v>
       </c>
       <c r="K15" s="23" t="n">
         <v>6000</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" s="12" t="n"/>
       <c r="Z15" s="8" t="n">
-        <v>6</v>
+        <v>4.026845637583893</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
       <c r="H16" s="22" t="n"/>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n">
-        <v>1000</v>
+        <v>1490</v>
       </c>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
@@ -2281,7 +2281,7 @@
         <v>6000</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>1000</v>
+        <v>1490</v>
       </c>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
@@ -2341,7 +2341,7 @@
         <v>4800</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>900</v>
+        <v>1341</v>
       </c>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
@@ -2401,7 +2401,7 @@
         <v>3000</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>950</v>
+        <v>1416</v>
       </c>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
@@ -2461,7 +2461,7 @@
         <v>9000</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>900</v>
+        <v>1341</v>
       </c>
       <c r="K20" s="23" t="n">
         <v>4500</v>
@@ -2499,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>5</v>
+        <v>3.355704697986577</v>
       </c>
     </row>
     <row r="21">
@@ -2537,7 +2537,7 @@
         <v>7500</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>1450</v>
+        <v>2160</v>
       </c>
       <c r="K21" s="23" t="n">
         <v>10000</v>
@@ -2575,7 +2575,7 @@
         <v>2</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>6.896551724137931</v>
+        <v>4.628558204119416</v>
       </c>
     </row>
     <row r="22">
@@ -2611,7 +2611,7 @@
         <v>7500</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>1550</v>
+        <v>2310</v>
       </c>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
@@ -2667,7 +2667,7 @@
       <c r="H23" s="22" t="n"/>
       <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n">
-        <v>1550</v>
+        <v>2310</v>
       </c>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
@@ -2725,7 +2725,7 @@
         <v>7500</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>1550</v>
+        <v>2310</v>
       </c>
       <c r="K24" s="23" t="n">
         <v>10000</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Y24" s="12" t="n"/>
       <c r="Z24" s="8" t="n">
-        <v>6.451612903225806</v>
+        <v>4.329941545789132</v>
       </c>
     </row>
     <row r="25">
@@ -2795,7 +2795,7 @@
       <c r="H25" s="22" t="n"/>
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n">
-        <v>1550</v>
+        <v>2310</v>
       </c>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
@@ -2853,7 +2853,7 @@
         <v>10500</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>1550</v>
+        <v>2310</v>
       </c>
       <c r="K26" s="23" t="n">
         <v>7500</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Y26" s="12" t="n"/>
       <c r="Z26" s="8" t="n">
-        <v>4.838709677419355</v>
+        <v>3.247456159341849</v>
       </c>
     </row>
     <row r="27">
@@ -2923,7 +2923,7 @@
       <c r="H27" s="22" t="n"/>
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="8" t="n">
-        <v>1550</v>
+        <v>2310</v>
       </c>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
@@ -2981,7 +2981,7 @@
         <v>10500</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>1550</v>
+        <v>2310</v>
       </c>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
@@ -3041,7 +3041,7 @@
         <v>9600</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>1650</v>
+        <v>2458</v>
       </c>
       <c r="K29" s="23" t="n">
         <v>12800</v>
@@ -3079,7 +3079,7 @@
         <v>1.969230769230769</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>7.757575757575758</v>
+        <v>5.20642668293675</v>
       </c>
     </row>
     <row r="30">
@@ -3117,7 +3117,7 @@
         <v>9600</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>1650</v>
+        <v>2458</v>
       </c>
       <c r="K30" s="23" t="n">
         <v>12800</v>
@@ -3155,7 +3155,7 @@
         <v>1.969230769230769</v>
       </c>
       <c r="Z30" s="8" t="n">
-        <v>7.757575757575758</v>
+        <v>5.20642668293675</v>
       </c>
     </row>
     <row r="31">
@@ -3193,7 +3193,7 @@
         <v>9600</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>1650</v>
+        <v>2458</v>
       </c>
       <c r="K31" s="23" t="n">
         <v>10100</v>
@@ -3231,7 +3231,7 @@
         <v>1.553846153846154</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>6.121212121212121</v>
+        <v>4.10819605450478</v>
       </c>
     </row>
     <row r="32">
@@ -3269,7 +3269,7 @@
         <v>9600</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>1650</v>
+        <v>2458</v>
       </c>
       <c r="K32" s="23" t="n">
         <v>9600</v>
@@ -3307,7 +3307,7 @@
         <v>1.476923076923077</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>5.818181818181818</v>
+        <v>3.904820012202562</v>
       </c>
     </row>
     <row r="33">
@@ -3343,7 +3343,7 @@
         <v>9600</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>1950</v>
+        <v>2906</v>
       </c>
       <c r="K33" s="23" t="n">
         <v>16000</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="Y33" s="12" t="n"/>
       <c r="Z33" s="8" t="n">
-        <v>8.205128205128204</v>
+        <v>5.506797453106178</v>
       </c>
     </row>
     <row r="34">
@@ -3417,7 +3417,7 @@
         <v>9600</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>1850</v>
+        <v>2756</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>12800</v>
@@ -3461,7 +3461,7 @@
         <v>4.938461538461539</v>
       </c>
       <c r="Z34" s="8" t="n">
-        <v>17.35135135135135</v>
+        <v>11.6452022492291</v>
       </c>
     </row>
     <row r="35">
@@ -3499,7 +3499,7 @@
         <v>9600</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>1850</v>
+        <v>2756</v>
       </c>
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="8" t="n"/>
@@ -3559,7 +3559,7 @@
         <v>10000</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>650</v>
+        <v>968</v>
       </c>
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="n"/>
@@ -3603,7 +3603,7 @@
       <c r="H37" s="22" t="n"/>
       <c r="I37" s="8" t="n"/>
       <c r="J37" s="8" t="n">
-        <v>765</v>
+        <v>1140</v>
       </c>
       <c r="K37" s="23" t="n">
         <v>6000</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Y37" s="12" t="n"/>
       <c r="Z37" s="8" t="n">
-        <v>7.84313725490196</v>
+        <v>5.263850506645611</v>
       </c>
     </row>
     <row r="38">
@@ -3675,7 +3675,7 @@
         <v>4000</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="8" t="n"/>
@@ -3759,7 +3759,7 @@
         <v>4000</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>1150</v>
+        <v>1713</v>
       </c>
       <c r="K40" s="23" t="n">
         <v>3000</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="Y40" s="12" t="n"/>
       <c r="Z40" s="8" t="n">
-        <v>2.608695652173913</v>
+        <v>1.750802451123432</v>
       </c>
     </row>
     <row r="41">
@@ -3833,7 +3833,7 @@
         <v>3000</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>600</v>
+        <v>894</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>4000</v>
@@ -3877,7 +3877,7 @@
         <v>3.63</v>
       </c>
       <c r="Z41" s="8" t="n">
-        <v>30.25</v>
+        <v>20.30201342281879</v>
       </c>
     </row>
     <row r="42">
@@ -3915,7 +3915,7 @@
         <v>6000</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>1900</v>
+        <v>2831</v>
       </c>
       <c r="K42" s="23" t="n">
         <v>6000</v>
@@ -3953,7 +3953,7 @@
         <v>0.3</v>
       </c>
       <c r="Z42" s="8" t="n">
-        <v>3.157894736842105</v>
+        <v>2.119392440833628</v>
       </c>
     </row>
     <row r="43">
@@ -3987,7 +3987,7 @@
         <v>6000</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>1820</v>
+        <v>2712</v>
       </c>
       <c r="K43" s="23" t="n">
         <v>12000</v>
@@ -4025,7 +4025,7 @@
         <v>0.6</v>
       </c>
       <c r="Z43" s="8" t="n">
-        <v>6.593406593406593</v>
+        <v>4.425105096246035</v>
       </c>
     </row>
     <row r="44">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="n">
-        <v>400</v>
+        <v>596</v>
       </c>
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="8" t="n"/>
@@ -4117,7 +4117,7 @@
       <c r="H45" s="22" t="n"/>
       <c r="I45" s="8" t="n"/>
       <c r="J45" s="8" t="n">
-        <v>2850</v>
+        <v>4246</v>
       </c>
       <c r="K45" s="8" t="n"/>
       <c r="L45" s="8" t="n"/>
@@ -4223,7 +4223,7 @@
         <v>6000</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>1150</v>
+        <v>1713</v>
       </c>
       <c r="K47" s="23" t="n">
         <v>6000</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Y47" s="12" t="n"/>
       <c r="Z47" s="8" t="n">
-        <v>5.217391304347826</v>
+        <v>3.501604902246864</v>
       </c>
     </row>
     <row r="48">
@@ -4295,7 +4295,7 @@
         <v>7500</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K48" s="8" t="n"/>
       <c r="L48" s="8" t="n"/>
@@ -4353,7 +4353,7 @@
         <v>6000</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K49" s="23" t="n">
         <v>4000</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Y49" s="12" t="n"/>
       <c r="Z49" s="8" t="n">
-        <v>3.809523809523809</v>
+        <v>2.556727388942154</v>
       </c>
     </row>
     <row r="50">
@@ -4425,7 +4425,7 @@
         <v>6000</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K50" s="23" t="n">
         <v>6500</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Y50" s="12" t="n"/>
       <c r="Z50" s="8" t="n">
-        <v>6.190476190476191</v>
+        <v>4.154682007031</v>
       </c>
     </row>
     <row r="51">
@@ -4497,7 +4497,7 @@
         <v>6000</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="8" t="n"/>
@@ -4555,7 +4555,7 @@
         <v>6000</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K52" s="23" t="n">
         <v>6500</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Y52" s="12" t="n"/>
       <c r="Z52" s="8" t="n">
-        <v>6.190476190476191</v>
+        <v>4.154682007031</v>
       </c>
     </row>
     <row r="53">
@@ -4627,7 +4627,7 @@
         <v>6000</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K53" s="23" t="n">
         <v>4500</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="Y53" s="12" t="n"/>
       <c r="Z53" s="8" t="n">
-        <v>4.285714285714286</v>
+        <v>2.876318312559923</v>
       </c>
     </row>
     <row r="54">
@@ -4699,7 +4699,7 @@
         <v>6000</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K54" s="8" t="n">
         <v>4000</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="Y54" s="12" t="n"/>
       <c r="Z54" s="8" t="n">
-        <v>22.33333333333333</v>
+        <v>14.98881431767338</v>
       </c>
     </row>
     <row r="55">
@@ -4775,7 +4775,7 @@
       <c r="H55" s="22" t="n"/>
       <c r="I55" s="8" t="n"/>
       <c r="J55" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K55" s="23" t="n">
         <v>6000</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Y55" s="12" t="n"/>
       <c r="Z55" s="8" t="n">
-        <v>5.714285714285714</v>
+        <v>3.835091083413231</v>
       </c>
     </row>
     <row r="56">
@@ -4847,7 +4847,7 @@
         <v>6000</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K56" s="23" t="n">
         <v>4000</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="Y56" s="12" t="n"/>
       <c r="Z56" s="8" t="n">
-        <v>3.809523809523809</v>
+        <v>2.556727388942154</v>
       </c>
     </row>
     <row r="57">
@@ -4919,7 +4919,7 @@
         <v>6000</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K57" s="23" t="n">
         <v>4000</v>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="Y57" s="12" t="n"/>
       <c r="Z57" s="8" t="n">
-        <v>3.809523809523809</v>
+        <v>2.556727388942154</v>
       </c>
     </row>
     <row r="58">
@@ -4991,7 +4991,7 @@
         <v>6000</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>1050</v>
+        <v>1564</v>
       </c>
       <c r="K58" s="8" t="n">
         <v>4000</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Y58" s="12" t="n"/>
       <c r="Z58" s="8" t="n">
-        <v>22.76190476190476</v>
+        <v>15.27644614892937</v>
       </c>
     </row>
     <row r="59">
@@ -5069,7 +5069,7 @@
         <v>1250</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>300</v>
+        <v>447</v>
       </c>
       <c r="K59" s="23" t="n">
         <v>2500</v>
@@ -5107,7 +5107,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="Z59" s="8" t="n">
-        <v>8.333333333333334</v>
+        <v>5.592841163310962</v>
       </c>
     </row>
     <row r="60">
@@ -5189,7 +5189,7 @@
       <c r="H61" s="22" t="n"/>
       <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="n">
-        <v>1300</v>
+        <v>1937</v>
       </c>
       <c r="K61" s="23" t="n">
         <v>6400</v>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Y61" s="12" t="n"/>
       <c r="Z61" s="8" t="n">
-        <v>4.923076923076923</v>
+        <v>3.304078471863707</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -5293,7 +5293,7 @@
         <v>6000</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>550</v>
+        <v>820</v>
       </c>
       <c r="K63" s="23" t="n">
         <v>6000</v>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Y63" s="12" t="n"/>
       <c r="Z63" s="8" t="n">
-        <v>10.90909090909091</v>
+        <v>7.321537522879804</v>
       </c>
     </row>
     <row r="64">
@@ -5367,7 +5367,7 @@
         <v>6000</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="K64" s="23" t="n">
         <v>6000</v>
@@ -5399,7 +5399,7 @@
         <v>1.5</v>
       </c>
       <c r="Z64" s="8" t="n">
-        <v>17.14285714285714</v>
+        <v>11.50527325023969</v>
       </c>
     </row>
     <row r="65">
@@ -5437,7 +5437,7 @@
         <v>4500</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="K65" s="8" t="n">
         <v>6000</v>
@@ -5485,7 +5485,7 @@
         <v>7.675</v>
       </c>
       <c r="Z65" s="8" t="n">
-        <v>87.71428571428571</v>
+        <v>58.8686481303931</v>
       </c>
     </row>
     <row r="66">
@@ -5523,7 +5523,7 @@
         <v>4500</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>1750</v>
+        <v>2608</v>
       </c>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
@@ -5575,7 +5575,7 @@
         <v>4500</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>1030</v>
+        <v>1535</v>
       </c>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
@@ -5635,7 +5635,7 @@
         <v>6000</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>385</v>
+        <v>574</v>
       </c>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
@@ -5695,7 +5695,7 @@
         <v>6000</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>620</v>
+        <v>924</v>
       </c>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="I70" s="8" t="n"/>
       <c r="J70" s="8" t="n">
-        <v>2750</v>
+        <v>4098</v>
       </c>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n">
-        <v>2750</v>
+        <v>4098</v>
       </c>
       <c r="K71" s="23" t="n">
         <v>9600</v>
@@ -5837,7 +5837,7 @@
         <v>0.48</v>
       </c>
       <c r="Z71" s="8" t="n">
-        <v>3.490909090909091</v>
+        <v>2.342892007321538</v>
       </c>
     </row>
     <row r="72">
@@ -5875,7 +5875,7 @@
         <v>10000</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>760</v>
+        <v>1132</v>
       </c>
       <c r="K72" s="8" t="n"/>
       <c r="L72" s="8" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="n">
-        <v>2850</v>
+        <v>4246</v>
       </c>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="I74" s="8" t="n"/>
       <c r="J74" s="8" t="n">
-        <v>2850</v>
+        <v>4246</v>
       </c>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
@@ -6065,7 +6065,7 @@
         <v>9600</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>2750</v>
+        <v>4098</v>
       </c>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
@@ -6119,7 +6119,7 @@
         <v>9600</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>2750</v>
+        <v>4098</v>
       </c>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
@@ -6169,7 +6169,7 @@
       <c r="H78" s="22" t="n"/>
       <c r="I78" s="8" t="n"/>
       <c r="J78" s="8" t="n">
-        <v>3500</v>
+        <v>5215</v>
       </c>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
@@ -6225,7 +6225,7 @@
       <c r="H79" s="22" t="n"/>
       <c r="I79" s="8" t="n"/>
       <c r="J79" s="8" t="n">
-        <v>2900</v>
+        <v>4321</v>
       </c>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="23" t="n">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="Y79" s="12" t="n"/>
       <c r="Z79" s="8" t="n">
-        <v>6.068965517241379</v>
+        <v>4.073131219625087</v>
       </c>
     </row>
     <row r="80">
@@ -6299,7 +6299,7 @@
       <c r="H80" s="22" t="n"/>
       <c r="I80" s="8" t="n"/>
       <c r="J80" s="8" t="n">
-        <v>2700</v>
+        <v>4023</v>
       </c>
       <c r="K80" s="8" t="n"/>
       <c r="L80" s="8" t="n"/>
@@ -6351,7 +6351,7 @@
       <c r="H81" s="22" t="n"/>
       <c r="I81" s="8" t="n"/>
       <c r="J81" s="8" t="n">
-        <v>4650</v>
+        <v>6929</v>
       </c>
       <c r="K81" s="8" t="n"/>
       <c r="L81" s="8" t="n">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Y81" s="12" t="n"/>
       <c r="Z81" s="8" t="n">
-        <v>24.97849462365591</v>
+        <v>16.76409035144692</v>
       </c>
     </row>
     <row r="82">
@@ -6423,7 +6423,7 @@
       <c r="H82" s="22" t="n"/>
       <c r="I82" s="8" t="n"/>
       <c r="J82" s="8" t="n">
-        <v>6000</v>
+        <v>8940</v>
       </c>
       <c r="K82" s="8" t="n">
         <v>27500</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="Y82" s="12" t="n"/>
       <c r="Z82" s="8" t="n">
-        <v>17.65</v>
+        <v>11.84563758389262</v>
       </c>
     </row>
     <row r="83">
@@ -6545,7 +6545,7 @@
       <c r="H84" s="22" t="n"/>
       <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="K84" s="23" t="n">
         <v>17500</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Y84" s="12" t="n"/>
       <c r="Z84" s="8" t="n">
-        <v>211.3526570048309</v>
+        <v>100.1144164759725</v>
       </c>
     </row>
     <row r="85">
@@ -6619,7 +6619,7 @@
         <v>27000</v>
       </c>
       <c r="J85" s="8" t="n">
-        <v>8000</v>
+        <v>11920</v>
       </c>
       <c r="K85" s="23" t="n">
         <v>29000</v>
@@ -6657,7 +6657,7 @@
         <v>1.16</v>
       </c>
       <c r="Z85" s="8" t="n">
-        <v>3.625</v>
+        <v>2.432885906040268</v>
       </c>
     </row>
     <row r="86">
@@ -6691,7 +6691,7 @@
         <v>27000</v>
       </c>
       <c r="J86" s="8" t="n">
-        <v>8000</v>
+        <v>11920</v>
       </c>
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
@@ -6747,7 +6747,7 @@
         <v>27000</v>
       </c>
       <c r="J87" s="8" t="n">
-        <v>8000</v>
+        <v>11920</v>
       </c>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="8" t="n"/>
@@ -6803,7 +6803,7 @@
       <c r="H88" s="22" t="n"/>
       <c r="I88" s="8" t="n"/>
       <c r="J88" s="8" t="n">
-        <v>10000</v>
+        <v>14900</v>
       </c>
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
@@ -6863,7 +6863,7 @@
         <v>34000</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>12500</v>
+        <v>18625</v>
       </c>
       <c r="K89" s="8" t="n">
         <v>40000</v>
@@ -6907,7 +6907,7 @@
         <v>1.613333333333333</v>
       </c>
       <c r="Z89" s="8" t="n">
-        <v>3.872</v>
+        <v>2.598657718120805</v>
       </c>
     </row>
     <row r="90">
@@ -6937,7 +6937,7 @@
       <c r="H90" s="22" t="n"/>
       <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n">
-        <v>14000</v>
+        <v>20860</v>
       </c>
       <c r="K90" s="23" t="n">
         <v>55000</v>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="Y90" s="12" t="n"/>
       <c r="Z90" s="8" t="n">
-        <v>3.928571428571428</v>
+        <v>2.636625119846596</v>
       </c>
     </row>
     <row r="91">
@@ -7155,7 +7155,7 @@
         <v>22500</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>6000</v>
+        <v>8940</v>
       </c>
       <c r="K94" s="23" t="n">
         <v>27500</v>
@@ -7199,7 +7199,7 @@
         <v>1.375</v>
       </c>
       <c r="Z94" s="8" t="n">
-        <v>4.583333333333333</v>
+        <v>3.076062639821029</v>
       </c>
     </row>
     <row r="95">
@@ -7233,7 +7233,7 @@
       <c r="H95" s="22" t="n"/>
       <c r="I95" s="8" t="n"/>
       <c r="J95" s="8" t="n">
-        <v>143</v>
+        <v>302</v>
       </c>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
@@ -7290,7 +7290,9 @@
         <v>35000</v>
       </c>
       <c r="I96" s="8" t="n"/>
-      <c r="J96" s="8" t="n"/>
+      <c r="J96" s="8" t="n">
+        <v>455</v>
+      </c>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
@@ -7344,7 +7346,9 @@
       </c>
       <c r="H97" s="22" t="n"/>
       <c r="I97" s="8" t="n"/>
-      <c r="J97" s="8" t="n"/>
+      <c r="J97" s="8" t="n">
+        <v>2314</v>
+      </c>
       <c r="K97" s="8" t="n">
         <v>23000</v>
       </c>
@@ -7382,7 +7386,9 @@
         <v>2373</v>
       </c>
       <c r="Y97" s="12" t="n"/>
-      <c r="Z97" s="8" t="n"/>
+      <c r="Z97" s="8" t="n">
+        <v>18.25410544511668</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -7415,7 +7421,7 @@
       <c r="H98" s="22" t="n"/>
       <c r="I98" s="8" t="n"/>
       <c r="J98" s="8" t="n">
-        <v>297</v>
+        <v>627</v>
       </c>
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
@@ -7471,7 +7477,7 @@
       <c r="H99" s="22" t="n"/>
       <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n">
-        <v>176</v>
+        <v>372</v>
       </c>
       <c r="K99" s="23" t="n">
         <v>28000</v>
@@ -7507,7 +7513,7 @@
       </c>
       <c r="Y99" s="12" t="n"/>
       <c r="Z99" s="8" t="n">
-        <v>158.7301587301587</v>
+        <v>75.18796992481202</v>
       </c>
     </row>
     <row r="100">
@@ -7542,7 +7548,9 @@
         <v>55000</v>
       </c>
       <c r="I100" s="8" t="n"/>
-      <c r="J100" s="8" t="n"/>
+      <c r="J100" s="8" t="n">
+        <v>1261</v>
+      </c>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
@@ -7593,7 +7601,7 @@
       <c r="H101" s="22" t="n"/>
       <c r="I101" s="8" t="n"/>
       <c r="J101" s="8" t="n">
-        <v>14400</v>
+        <v>21456</v>
       </c>
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="8" t="n"/>
@@ -7653,7 +7661,7 @@
         <v>37500</v>
       </c>
       <c r="J102" s="8" t="n">
-        <v>23000</v>
+        <v>34270</v>
       </c>
       <c r="K102" s="8" t="n">
         <v>45000</v>
@@ -7695,7 +7703,7 @@
         <v>1.76</v>
       </c>
       <c r="Z102" s="8" t="n">
-        <v>4.208695652173913</v>
+        <v>2.824627954479136</v>
       </c>
     </row>
     <row r="103">
@@ -7731,7 +7739,7 @@
       </c>
       <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n">
-        <v>23000</v>
+        <v>34270</v>
       </c>
       <c r="K103" s="23" t="n">
         <v>56200</v>
@@ -7769,7 +7777,7 @@
         <v>1.021818181818182</v>
       </c>
       <c r="Z103" s="8" t="n">
-        <v>2.443478260869565</v>
+        <v>1.639918295885614</v>
       </c>
     </row>
     <row r="104">
@@ -7801,7 +7809,7 @@
       </c>
       <c r="I104" s="8" t="n"/>
       <c r="J104" s="8" t="n">
-        <v>23000</v>
+        <v>34270</v>
       </c>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
@@ -7855,7 +7863,7 @@
         <v>150000</v>
       </c>
       <c r="J105" s="8" t="n">
-        <v>55000</v>
+        <v>81950</v>
       </c>
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
@@ -7939,7 +7947,7 @@
         <v>26000</v>
       </c>
       <c r="J107" s="8" t="n">
-        <v>5750</v>
+        <v>8568</v>
       </c>
       <c r="K107" s="23" t="n">
         <v>32000</v>
@@ -7975,7 +7983,7 @@
       </c>
       <c r="Y107" s="12" t="n"/>
       <c r="Z107" s="8" t="n">
-        <v>5.565217391304348</v>
+        <v>3.735045229063321</v>
       </c>
     </row>
     <row r="108">
@@ -8009,7 +8017,7 @@
       <c r="H108" s="22" t="n"/>
       <c r="I108" s="8" t="n"/>
       <c r="J108" s="8" t="n">
-        <v>5400</v>
+        <v>8046</v>
       </c>
       <c r="K108" s="23" t="n">
         <v>15000</v>
@@ -8045,7 +8053,7 @@
       </c>
       <c r="Y108" s="12" t="n"/>
       <c r="Z108" s="8" t="n">
-        <v>2.777777777777778</v>
+        <v>1.86428038777032</v>
       </c>
     </row>
     <row r="109">
@@ -8079,7 +8087,7 @@
       <c r="H109" s="22" t="n"/>
       <c r="I109" s="8" t="n"/>
       <c r="J109" s="8" t="n">
-        <v>6700</v>
+        <v>9983</v>
       </c>
       <c r="K109" s="23" t="n">
         <v>19500</v>
@@ -8115,7 +8123,7 @@
       </c>
       <c r="Y109" s="12" t="n"/>
       <c r="Z109" s="8" t="n">
-        <v>2.91044776119403</v>
+        <v>1.953320645096664</v>
       </c>
     </row>
     <row r="110">
@@ -8149,7 +8157,7 @@
       <c r="H110" s="22" t="n"/>
       <c r="I110" s="8" t="n"/>
       <c r="J110" s="8" t="n">
-        <v>1800</v>
+        <v>2682</v>
       </c>
       <c r="K110" s="23" t="n">
         <v>9750</v>
@@ -8185,7 +8193,7 @@
       </c>
       <c r="Y110" s="12" t="n"/>
       <c r="Z110" s="8" t="n">
-        <v>5.416666666666667</v>
+        <v>3.635346756152125</v>
       </c>
     </row>
     <row r="111">
@@ -8221,7 +8229,7 @@
         <v>35000</v>
       </c>
       <c r="J111" s="8" t="n">
-        <v>11250</v>
+        <v>16762</v>
       </c>
       <c r="K111" s="23" t="n">
         <v>39000</v>
@@ -8257,7 +8265,7 @@
       </c>
       <c r="Y111" s="12" t="n"/>
       <c r="Z111" s="8" t="n">
-        <v>3.466666666666667</v>
+        <v>2.32662192393736</v>
       </c>
     </row>
     <row r="112">
@@ -8293,7 +8301,7 @@
         <v>45000</v>
       </c>
       <c r="J112" s="8" t="n">
-        <v>18000</v>
+        <v>26820</v>
       </c>
       <c r="K112" s="23" t="n">
         <v>80000</v>
@@ -8329,7 +8337,7 @@
       </c>
       <c r="Y112" s="12" t="n"/>
       <c r="Z112" s="8" t="n">
-        <v>4.444444444444445</v>
+        <v>2.982848620432513</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -8391,7 +8399,7 @@
       <c r="H114" s="22" t="n"/>
       <c r="I114" s="8" t="n"/>
       <c r="J114" s="8" t="n">
-        <v>4250</v>
+        <v>6332</v>
       </c>
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
@@ -8437,7 +8445,7 @@
       <c r="H115" s="22" t="n"/>
       <c r="I115" s="8" t="n"/>
       <c r="J115" s="8" t="n">
-        <v>6100</v>
+        <v>9089</v>
       </c>
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="8" t="n"/>
@@ -8485,7 +8493,7 @@
         <v>24000</v>
       </c>
       <c r="J116" s="8" t="n">
-        <v>10950</v>
+        <v>16315</v>
       </c>
       <c r="K116" s="8" t="n">
         <v>30000</v>
@@ -8527,7 +8535,7 @@
       </c>
       <c r="Y116" s="12" t="n"/>
       <c r="Z116" s="8" t="n">
-        <v>3.143947900291938</v>
+        <v>2.110032147846939</v>
       </c>
     </row>
     <row r="117">
@@ -8557,7 +8565,7 @@
       <c r="H117" s="22" t="n"/>
       <c r="I117" s="8" t="n"/>
       <c r="J117" s="8" t="n">
-        <v>14150</v>
+        <v>21084</v>
       </c>
       <c r="K117" s="8" t="n">
         <v>37500</v>
@@ -8601,7 +8609,7 @@
       </c>
       <c r="Y117" s="12" t="n"/>
       <c r="Z117" s="8" t="n">
-        <v>13.37102473498233</v>
+        <v>8.973842104014988</v>
       </c>
     </row>
     <row r="118">
@@ -8631,7 +8639,7 @@
       <c r="H118" s="22" t="n"/>
       <c r="I118" s="8" t="n"/>
       <c r="J118" s="8" t="n">
-        <v>18600</v>
+        <v>27714</v>
       </c>
       <c r="K118" s="8" t="n"/>
       <c r="L118" s="8" t="n"/>
@@ -8665,7 +8673,7 @@
       </c>
       <c r="Y118" s="12" t="n"/>
       <c r="Z118" s="8" t="n">
-        <v>11.88978494623656</v>
+        <v>7.97972144042722</v>
       </c>
     </row>
     <row r="119">
@@ -8699,7 +8707,7 @@
         <v>150000</v>
       </c>
       <c r="J119" s="8" t="n">
-        <v>44000</v>
+        <v>65560</v>
       </c>
       <c r="K119" s="23" t="n">
         <v>150000</v>
@@ -8743,7 +8751,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="Z119" s="8" t="n">
-        <v>3.409090909090909</v>
+        <v>2.287980475899939</v>
       </c>
     </row>
     <row r="120">
@@ -8777,7 +8785,7 @@
         <v>200000</v>
       </c>
       <c r="J120" s="8" t="n">
-        <v>62500</v>
+        <v>93125</v>
       </c>
       <c r="K120" s="8" t="n">
         <v>150000</v>
@@ -8821,7 +8829,7 @@
         <v>1.092896174863388</v>
       </c>
       <c r="Z120" s="8" t="n">
-        <v>2.622950819672131</v>
+        <v>1.760369677632303</v>
       </c>
     </row>
     <row r="121">
@@ -8851,7 +8859,7 @@
       <c r="H121" s="22" t="n"/>
       <c r="I121" s="8" t="n"/>
       <c r="J121" s="8" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="K121" s="23" t="n">
         <v>75000</v>
@@ -8887,7 +8895,7 @@
       </c>
       <c r="Y121" s="12" t="n"/>
       <c r="Z121" s="8" t="n">
-        <v>166.6666666666667</v>
+        <v>78.94736842105263</v>
       </c>
     </row>
     <row r="122">
@@ -8921,7 +8929,7 @@
         <v>250000</v>
       </c>
       <c r="J122" s="8" t="n">
-        <v>96000</v>
+        <v>143040</v>
       </c>
       <c r="K122" s="8" t="n"/>
       <c r="L122" s="8" t="n"/>
@@ -8959,7 +8967,7 @@
         <v>2.9405</v>
       </c>
       <c r="Z122" s="8" t="n">
-        <v>6.126041666666667</v>
+        <v>4.111437360178971</v>
       </c>
     </row>
     <row r="123">
@@ -8993,7 +9001,7 @@
         <v>300000</v>
       </c>
       <c r="J123" s="8" t="n">
-        <v>114000</v>
+        <v>169860</v>
       </c>
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
@@ -9075,7 +9083,7 @@
       <c r="H125" s="22" t="n"/>
       <c r="I125" s="8" t="n"/>
       <c r="J125" s="8" t="n">
-        <v>4250</v>
+        <v>6332</v>
       </c>
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
@@ -9131,7 +9139,7 @@
       <c r="H126" s="22" t="n"/>
       <c r="I126" s="8" t="n"/>
       <c r="J126" s="8" t="n">
-        <v>4600</v>
+        <v>6854</v>
       </c>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
@@ -9253,7 +9261,7 @@
       <c r="H128" s="22" t="n"/>
       <c r="I128" s="8" t="n"/>
       <c r="J128" s="8" t="n">
-        <v>11000</v>
+        <v>16390</v>
       </c>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
@@ -9303,7 +9311,7 @@
         <v>120000</v>
       </c>
       <c r="J129" s="8" t="n">
-        <v>21000</v>
+        <v>31290</v>
       </c>
       <c r="K129" s="8" t="n"/>
       <c r="L129" s="8" t="n"/>
@@ -9341,7 +9349,7 @@
         <v>1.261034047919294</v>
       </c>
       <c r="Z129" s="8" t="n">
-        <v>3.9032006245121</v>
+        <v>2.619597734571879</v>
       </c>
     </row>
     <row r="130">
@@ -9379,7 +9387,7 @@
         <v>120000</v>
       </c>
       <c r="J130" s="8" t="n">
-        <v>22500</v>
+        <v>33525</v>
       </c>
       <c r="K130" s="23" t="n">
         <v>90000</v>
@@ -9417,7 +9425,7 @@
         <v>1.5</v>
       </c>
       <c r="Z130" s="8" t="n">
-        <v>4</v>
+        <v>2.684563758389262</v>
       </c>
     </row>
     <row r="131">
@@ -9451,7 +9459,7 @@
         <v>150000</v>
       </c>
       <c r="J131" s="8" t="n">
-        <v>32000</v>
+        <v>47680</v>
       </c>
       <c r="K131" s="8" t="n"/>
       <c r="L131" s="8" t="n"/>
@@ -9499,7 +9507,7 @@
       </c>
       <c r="I132" s="8" t="n"/>
       <c r="J132" s="8" t="n">
-        <v>74000</v>
+        <v>110260</v>
       </c>
       <c r="K132" s="23" t="n">
         <v>250000</v>
@@ -9541,7 +9549,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="Z132" s="8" t="n">
-        <v>3.378378378378379</v>
+        <v>2.26736803918012</v>
       </c>
     </row>
     <row r="133">
@@ -9575,7 +9583,7 @@
         <v>400000</v>
       </c>
       <c r="J133" s="8" t="n">
-        <v>86000</v>
+        <v>128140</v>
       </c>
       <c r="K133" s="8" t="n"/>
       <c r="L133" s="23" t="n">
@@ -9607,7 +9615,7 @@
         <v>1.554666666666667</v>
       </c>
       <c r="Z133" s="8" t="n">
-        <v>5.423255813953489</v>
+        <v>3.639769002653348</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -9673,7 +9681,7 @@
       <c r="H135" s="22" t="n"/>
       <c r="I135" s="8" t="n"/>
       <c r="J135" s="8" t="n">
-        <v>5600</v>
+        <v>8344</v>
       </c>
       <c r="K135" s="8" t="n"/>
       <c r="L135" s="8" t="n"/>
@@ -9733,7 +9741,7 @@
         <v>17500</v>
       </c>
       <c r="J136" s="8" t="n">
-        <v>5500</v>
+        <v>8195</v>
       </c>
       <c r="K136" s="23" t="n">
         <v>22500</v>
@@ -9771,7 +9779,7 @@
         <v>1.125</v>
       </c>
       <c r="Z136" s="8" t="n">
-        <v>4.090909090909091</v>
+        <v>2.745576571079927</v>
       </c>
     </row>
     <row r="137">
@@ -9805,7 +9813,7 @@
         <v>17500</v>
       </c>
       <c r="J137" s="8" t="n">
-        <v>4700</v>
+        <v>7003</v>
       </c>
       <c r="K137" s="23" t="n">
         <v>30000</v>
@@ -9843,7 +9851,7 @@
         <v>1.5</v>
       </c>
       <c r="Z137" s="8" t="n">
-        <v>6.382978723404255</v>
+        <v>4.283878337855205</v>
       </c>
     </row>
     <row r="138">
@@ -9881,7 +9889,7 @@
         <v>32000</v>
       </c>
       <c r="J138" s="8" t="n">
-        <v>9500</v>
+        <v>14155</v>
       </c>
       <c r="K138" s="8" t="n"/>
       <c r="L138" s="8" t="n"/>
@@ -9935,7 +9943,7 @@
         <v>32000</v>
       </c>
       <c r="J139" s="8" t="n">
-        <v>9500</v>
+        <v>14155</v>
       </c>
       <c r="K139" s="8" t="n"/>
       <c r="L139" s="8" t="n"/>
@@ -10017,7 +10025,7 @@
       <c r="H141" s="22" t="n"/>
       <c r="I141" s="8" t="n"/>
       <c r="J141" s="8" t="n">
-        <v>800</v>
+        <v>1016</v>
       </c>
       <c r="K141" s="8" t="n"/>
       <c r="L141" s="8" t="n"/>
@@ -10067,7 +10075,7 @@
       <c r="H142" s="22" t="n"/>
       <c r="I142" s="8" t="n"/>
       <c r="J142" s="8" t="n">
-        <v>750</v>
+        <v>952</v>
       </c>
       <c r="K142" s="8" t="n"/>
       <c r="L142" s="8" t="n"/>
@@ -10117,7 +10125,7 @@
       <c r="H143" s="22" t="n"/>
       <c r="I143" s="8" t="n"/>
       <c r="J143" s="8" t="n">
-        <v>5600</v>
+        <v>7112</v>
       </c>
       <c r="K143" s="8" t="n"/>
       <c r="L143" s="8" t="n"/>
@@ -10167,7 +10175,7 @@
       <c r="H144" s="22" t="n"/>
       <c r="I144" s="8" t="n"/>
       <c r="J144" s="8" t="n">
-        <v>9100</v>
+        <v>11557</v>
       </c>
       <c r="K144" s="8" t="n"/>
       <c r="L144" s="8" t="n"/>
@@ -10217,7 +10225,7 @@
       <c r="H145" s="22" t="n"/>
       <c r="I145" s="8" t="n"/>
       <c r="J145" s="8" t="n">
-        <v>276</v>
+        <v>754</v>
       </c>
       <c r="K145" s="8" t="n"/>
       <c r="L145" s="8" t="n"/>
@@ -10267,7 +10275,7 @@
       <c r="H146" s="22" t="n"/>
       <c r="I146" s="8" t="n"/>
       <c r="J146" s="8" t="n">
-        <v>256</v>
+        <v>702</v>
       </c>
       <c r="K146" s="8" t="n"/>
       <c r="L146" s="8" t="n"/>
@@ -10317,7 +10325,7 @@
       <c r="H147" s="22" t="n"/>
       <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n">
-        <v>361</v>
+        <v>988</v>
       </c>
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
@@ -10367,7 +10375,7 @@
       <c r="H148" s="22" t="n"/>
       <c r="I148" s="8" t="n"/>
       <c r="J148" s="8" t="n">
-        <v>446</v>
+        <v>1222</v>
       </c>
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>
@@ -10451,7 +10459,7 @@
         <v>6000</v>
       </c>
       <c r="J150" s="8" t="n">
-        <v>750</v>
+        <v>1118</v>
       </c>
       <c r="K150" s="8" t="n"/>
       <c r="L150" s="8" t="n"/>
@@ -10507,7 +10515,7 @@
         <v>6000</v>
       </c>
       <c r="J151" s="8" t="n">
-        <v>3300</v>
+        <v>4917</v>
       </c>
       <c r="K151" s="23" t="n">
         <v>9000</v>
@@ -10545,7 +10553,7 @@
         <v>0.75</v>
       </c>
       <c r="Z151" s="8" t="n">
-        <v>2.727272727272727</v>
+        <v>1.830384380719951</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -10615,7 +10623,7 @@
         <v>25000</v>
       </c>
       <c r="J153" s="8" t="n">
-        <v>5250</v>
+        <v>7822</v>
       </c>
       <c r="K153" s="8" t="n"/>
       <c r="L153" s="8" t="n"/>
@@ -10673,7 +10681,7 @@
         <v>25000</v>
       </c>
       <c r="J154" s="8" t="n">
-        <v>5600</v>
+        <v>8344</v>
       </c>
       <c r="K154" s="23" t="n">
         <v>25000</v>
@@ -10709,7 +10717,7 @@
       </c>
       <c r="Y154" s="12" t="n"/>
       <c r="Z154" s="8" t="n">
-        <v>4.464285714285714</v>
+        <v>2.996164908916587</v>
       </c>
     </row>
     <row r="155">
@@ -10745,7 +10753,7 @@
         <v>40000</v>
       </c>
       <c r="J155" s="8" t="n">
-        <v>16850</v>
+        <v>25107</v>
       </c>
       <c r="K155" s="8" t="n"/>
       <c r="L155" s="8" t="n"/>
@@ -10799,7 +10807,7 @@
         <v>40000</v>
       </c>
       <c r="J156" s="8" t="n">
-        <v>11000</v>
+        <v>16390</v>
       </c>
       <c r="K156" s="8" t="n"/>
       <c r="L156" s="8" t="n"/>
@@ -10853,7 +10861,7 @@
         <v>40000</v>
       </c>
       <c r="J157" s="8" t="n">
-        <v>11800</v>
+        <v>17582</v>
       </c>
       <c r="K157" s="8" t="n"/>
       <c r="L157" s="23" t="n">
@@ -10885,7 +10893,7 @@
         <v>1.87</v>
       </c>
       <c r="Z157" s="8" t="n">
-        <v>6.338983050847458</v>
+        <v>4.25435104083722</v>
       </c>
     </row>
     <row r="158">
@@ -10923,7 +10931,7 @@
         <v>40000</v>
       </c>
       <c r="J158" s="8" t="n">
-        <v>13000</v>
+        <v>19370</v>
       </c>
       <c r="K158" s="8" t="n"/>
       <c r="L158" s="8" t="n"/>
@@ -11005,7 +11013,7 @@
         <v>35000</v>
       </c>
       <c r="J160" s="8" t="n">
-        <v>15000</v>
+        <v>22350</v>
       </c>
       <c r="K160" s="23" t="n">
         <v>60000</v>
@@ -11049,7 +11057,7 @@
         <v>2.4</v>
       </c>
       <c r="Z160" s="8" t="n">
-        <v>4</v>
+        <v>2.684563758389262</v>
       </c>
     </row>
     <row r="161">
@@ -11081,7 +11089,7 @@
       </c>
       <c r="I161" s="8" t="n"/>
       <c r="J161" s="8" t="n">
-        <v>20500</v>
+        <v>30545</v>
       </c>
       <c r="K161" s="23" t="n">
         <v>90000</v>
@@ -11123,7 +11131,7 @@
         <v>2.571428571428572</v>
       </c>
       <c r="Z161" s="8" t="n">
-        <v>4.390243902439025</v>
+        <v>2.946472417744312</v>
       </c>
     </row>
     <row r="162">
@@ -11157,7 +11165,7 @@
         <v>44000</v>
       </c>
       <c r="J162" s="8" t="n">
-        <v>23800</v>
+        <v>35462</v>
       </c>
       <c r="K162" s="8" t="n">
         <v>57600</v>
@@ -11201,7 +11209,7 @@
         <v>2.388571428571429</v>
       </c>
       <c r="Z162" s="8" t="n">
-        <v>3.512605042016807</v>
+        <v>2.357453048333428</v>
       </c>
     </row>
     <row r="163">
@@ -11233,7 +11241,7 @@
       </c>
       <c r="I163" s="8" t="n"/>
       <c r="J163" s="8" t="n">
-        <v>34000</v>
+        <v>50660</v>
       </c>
       <c r="K163" s="8" t="n">
         <v>84000</v>
@@ -11275,7 +11283,7 @@
         <v>1.713859910581222</v>
       </c>
       <c r="Z163" s="8" t="n">
-        <v>2.772420443587271</v>
+        <v>1.860684861467967</v>
       </c>
     </row>
     <row r="164">
@@ -11307,7 +11315,7 @@
       </c>
       <c r="I164" s="8" t="n"/>
       <c r="J164" s="8" t="n">
-        <v>45250</v>
+        <v>67422</v>
       </c>
       <c r="K164" s="8" t="n"/>
       <c r="L164" s="23" t="n">
@@ -11349,7 +11357,7 @@
         <v>1.65</v>
       </c>
       <c r="Z164" s="8" t="n">
-        <v>2.917127071823205</v>
+        <v>1.957803403908191</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -11469,7 +11477,7 @@
         <v>4000</v>
       </c>
       <c r="J167" s="8" t="n">
-        <v>600</v>
+        <v>894</v>
       </c>
       <c r="K167" s="23" t="n">
         <v>9000</v>
@@ -11507,7 +11515,7 @@
         <v>1.8</v>
       </c>
       <c r="Z167" s="8" t="n">
-        <v>15</v>
+        <v>10.06711409395973</v>
       </c>
     </row>
     <row r="168">
@@ -11545,7 +11553,7 @@
         <v>9000</v>
       </c>
       <c r="J168" s="8" t="n">
-        <v>1400</v>
+        <v>2086</v>
       </c>
       <c r="K168" s="8" t="n"/>
       <c r="L168" s="8" t="n"/>
@@ -11605,7 +11613,7 @@
         <v>9000</v>
       </c>
       <c r="J169" s="8" t="n">
-        <v>900</v>
+        <v>1341</v>
       </c>
       <c r="K169" s="23" t="n">
         <v>8000</v>
@@ -11643,7 +11651,7 @@
         <v>1.333333333333333</v>
       </c>
       <c r="Z169" s="8" t="n">
-        <v>8.888888888888889</v>
+        <v>5.965697240865026</v>
       </c>
     </row>
     <row r="170">
@@ -11679,7 +11687,7 @@
         <v>9600</v>
       </c>
       <c r="J170" s="8" t="n">
-        <v>2500</v>
+        <v>3725</v>
       </c>
       <c r="K170" s="23" t="n">
         <v>16000</v>
@@ -11715,7 +11723,7 @@
       </c>
       <c r="Y170" s="12" t="n"/>
       <c r="Z170" s="8" t="n">
-        <v>6.4</v>
+        <v>4.295302013422819</v>
       </c>
     </row>
     <row r="171">
@@ -11753,7 +11761,7 @@
         <v>14400</v>
       </c>
       <c r="J171" s="8" t="n">
-        <v>2050</v>
+        <v>3054</v>
       </c>
       <c r="K171" s="23" t="n">
         <v>14400</v>
@@ -11795,7 +11803,7 @@
         <v>2.215384615384616</v>
       </c>
       <c r="Z171" s="8" t="n">
-        <v>7.024390243902439</v>
+        <v>4.714355868390899</v>
       </c>
     </row>
     <row r="172">
@@ -11833,7 +11841,7 @@
         <v>14400</v>
       </c>
       <c r="J172" s="8" t="n">
-        <v>2050</v>
+        <v>3054</v>
       </c>
       <c r="K172" s="23" t="n">
         <v>9600</v>
@@ -11871,7 +11879,7 @@
         <v>1.476923076923077</v>
       </c>
       <c r="Z172" s="8" t="n">
-        <v>4.682926829268292</v>
+        <v>3.1429039122606</v>
       </c>
     </row>
     <row r="173">
@@ -11905,7 +11913,7 @@
       <c r="H173" s="22" t="n"/>
       <c r="I173" s="8" t="n"/>
       <c r="J173" s="8" t="n">
-        <v>4400</v>
+        <v>6556</v>
       </c>
       <c r="K173" s="23" t="n">
         <v>25000</v>
@@ -11941,7 +11949,7 @@
       </c>
       <c r="Y173" s="12" t="n"/>
       <c r="Z173" s="8" t="n">
-        <v>5.681818181818182</v>
+        <v>3.813300793166564</v>
       </c>
     </row>
     <row r="174">
@@ -11975,7 +11983,7 @@
       <c r="H174" s="22" t="n"/>
       <c r="I174" s="8" t="n"/>
       <c r="J174" s="8" t="n">
-        <v>8600</v>
+        <v>12814</v>
       </c>
       <c r="K174" s="23" t="n">
         <v>19500</v>
@@ -12011,7 +12019,7 @@
       </c>
       <c r="Y174" s="12" t="n"/>
       <c r="Z174" s="8" t="n">
-        <v>2.267441860465116</v>
+        <v>1.521773060714843</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -12077,7 +12085,7 @@
       <c r="H176" s="22" t="n"/>
       <c r="I176" s="8" t="n"/>
       <c r="J176" s="8" t="n">
-        <v>300</v>
+        <v>447</v>
       </c>
       <c r="K176" s="8" t="n"/>
       <c r="L176" s="8" t="n"/>
@@ -12127,7 +12135,7 @@
       <c r="H177" s="22" t="n"/>
       <c r="I177" s="8" t="n"/>
       <c r="J177" s="8" t="n">
-        <v>850</v>
+        <v>1266</v>
       </c>
       <c r="K177" s="8" t="n"/>
       <c r="L177" s="8" t="n"/>
@@ -12177,7 +12185,7 @@
       <c r="H178" s="22" t="n"/>
       <c r="I178" s="8" t="n"/>
       <c r="J178" s="8" t="n">
-        <v>750</v>
+        <v>1118</v>
       </c>
       <c r="K178" s="8" t="n"/>
       <c r="L178" s="8" t="n"/>
@@ -12227,7 +12235,7 @@
       <c r="H179" s="22" t="n"/>
       <c r="I179" s="8" t="n"/>
       <c r="J179" s="8" t="n">
-        <v>1250</v>
+        <v>1862</v>
       </c>
       <c r="K179" s="8" t="n"/>
       <c r="L179" s="8" t="n"/>
@@ -12311,7 +12319,7 @@
       </c>
       <c r="I181" s="8" t="n"/>
       <c r="J181" s="8" t="n">
-        <v>2800</v>
+        <v>4172</v>
       </c>
       <c r="K181" s="8" t="n"/>
       <c r="L181" s="8" t="n"/>
@@ -12363,7 +12371,7 @@
       </c>
       <c r="I182" s="8" t="n"/>
       <c r="J182" s="8" t="n">
-        <v>4400</v>
+        <v>6556</v>
       </c>
       <c r="K182" s="8" t="n"/>
       <c r="L182" s="8" t="n"/>
@@ -12449,7 +12457,7 @@
         <v>6000</v>
       </c>
       <c r="J184" s="8" t="n">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="K184" s="8" t="n"/>
       <c r="L184" s="8" t="n"/>
@@ -12503,7 +12511,7 @@
         <v>6000</v>
       </c>
       <c r="J185" s="8" t="n">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="K185" s="8" t="n"/>
       <c r="L185" s="8" t="n"/>
@@ -12555,7 +12563,7 @@
       </c>
       <c r="I186" s="8" t="n"/>
       <c r="J186" s="8" t="n">
-        <v>243</v>
+        <v>513</v>
       </c>
       <c r="K186" s="8" t="n"/>
       <c r="L186" s="8" t="n"/>
@@ -12645,7 +12653,7 @@
       </c>
       <c r="I188" s="8" t="n"/>
       <c r="J188" s="8" t="n">
-        <v>293</v>
+        <v>619</v>
       </c>
       <c r="K188" s="8" t="n"/>
       <c r="L188" s="8" t="n"/>
@@ -12729,7 +12737,7 @@
       </c>
       <c r="I190" s="8" t="n"/>
       <c r="J190" s="8" t="n">
-        <v>5800</v>
+        <v>8642</v>
       </c>
       <c r="K190" s="23" t="n">
         <v>12000</v>
@@ -12767,7 +12775,7 @@
         <v>0.48</v>
       </c>
       <c r="Z190" s="8" t="n">
-        <v>2.068965517241379</v>
+        <v>1.388567461235825</v>
       </c>
     </row>
     <row r="191">
@@ -12799,7 +12807,7 @@
       <c r="H191" s="22" t="n"/>
       <c r="I191" s="8" t="n"/>
       <c r="J191" s="8" t="n">
-        <v>6150</v>
+        <v>9164</v>
       </c>
       <c r="K191" s="8" t="n"/>
       <c r="L191" s="8" t="n"/>
@@ -12923,7 +12931,7 @@
         <v>12500</v>
       </c>
       <c r="J194" s="8" t="n">
-        <v>2750</v>
+        <v>4098</v>
       </c>
       <c r="K194" s="8" t="n">
         <v>12000</v>
@@ -12961,7 +12969,7 @@
         <v>1.466666666666667</v>
       </c>
       <c r="Z194" s="8" t="n">
-        <v>8</v>
+        <v>5.369127516778524</v>
       </c>
     </row>
     <row r="195">
@@ -12999,7 +13007,7 @@
         <v>12500</v>
       </c>
       <c r="J195" s="8" t="n">
-        <v>2750</v>
+        <v>4098</v>
       </c>
       <c r="K195" s="23" t="n">
         <v>18000</v>
@@ -13031,7 +13039,7 @@
         <v>1.2</v>
       </c>
       <c r="Z195" s="8" t="n">
-        <v>6.545454545454546</v>
+        <v>4.392922513727883</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -13093,7 +13101,7 @@
         <v>25000</v>
       </c>
       <c r="J197" s="8" t="n">
-        <v>2000</v>
+        <v>2980</v>
       </c>
       <c r="K197" s="23" t="n">
         <v>30000</v>
@@ -13123,7 +13131,7 @@
       </c>
       <c r="Y197" s="12" t="n"/>
       <c r="Z197" s="8" t="n">
-        <v>15</v>
+        <v>10.06711409395973</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -13191,7 +13199,7 @@
         <v>9000</v>
       </c>
       <c r="J199" s="8" t="n">
-        <v>1200</v>
+        <v>1788</v>
       </c>
       <c r="K199" s="8" t="n"/>
       <c r="L199" s="8" t="n"/>
@@ -13243,7 +13251,7 @@
         <v>9600</v>
       </c>
       <c r="J200" s="8" t="n">
-        <v>2350</v>
+        <v>3502</v>
       </c>
       <c r="K200" s="23" t="n">
         <v>9600</v>
@@ -13279,7 +13287,7 @@
       </c>
       <c r="Y200" s="12" t="n"/>
       <c r="Z200" s="8" t="n">
-        <v>4.085106382978723</v>
+        <v>2.741682136227331</v>
       </c>
     </row>
     <row r="201">
@@ -13311,7 +13319,7 @@
       <c r="H201" s="22" t="n"/>
       <c r="I201" s="8" t="n"/>
       <c r="J201" s="8" t="n">
-        <v>3400</v>
+        <v>5066</v>
       </c>
       <c r="K201" s="8" t="n"/>
       <c r="L201" s="8" t="n"/>
@@ -17370,7 +17378,7 @@
         <v>432</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F5" s="26" t="n">
         <v>2105</v>
@@ -17430,7 +17438,7 @@
         <v>1257</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>5000</v>
@@ -17490,7 +17498,7 @@
         <v>285</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>5263</v>
@@ -17550,7 +17558,7 @@
         <v>1290</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F8" s="26" t="n">
         <v>1562</v>
@@ -17610,7 +17618,7 @@
         <v>2818</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>1667</v>
@@ -17670,7 +17678,7 @@
         <v>512</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
@@ -17732,7 +17740,7 @@
         <v>7394</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1200</v>
@@ -17792,7 +17800,7 @@
         <v>2081</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F12" s="26" t="n">
         <v>1406</v>
@@ -17852,7 +17860,7 @@
         <v>100</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>1818</v>
@@ -17912,7 +17920,7 @@
         <v>401</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>500</v>
+        <v>635</v>
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
@@ -17976,7 +17984,7 @@
         <v>88</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1818</v>
@@ -18036,7 +18044,7 @@
         <v>171</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F16" s="26" t="n">
         <v>1818</v>
@@ -18096,7 +18104,7 @@
         <v>1886</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F17" s="26" t="n">
         <v>833</v>
@@ -18156,7 +18164,7 @@
         <v>142</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F18" s="26" t="n">
         <v>1786</v>
@@ -18216,7 +18224,7 @@
         <v>52</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
@@ -18280,7 +18288,7 @@
         <v>110</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F20" s="26" t="n">
         <v>4464</v>
@@ -18342,7 +18350,7 @@
         <v>258</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F21" s="26" t="n">
         <v>2000</v>
@@ -18402,7 +18410,7 @@
         <v>33</v>
       </c>
       <c r="E22" s="25" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F22" s="26" t="n">
         <v>1840</v>
@@ -18464,7 +18472,7 @@
         <v>24</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F23" s="26" t="n">
         <v>2155</v>
@@ -18524,7 +18532,7 @@
         <v>346</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F24" s="26" t="n">
         <v>2727</v>
@@ -18586,7 +18594,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
@@ -18650,7 +18658,7 @@
         <v>52</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
